--- a/Data/Input/Oresnik_statistika.xlsx
+++ b/Data/Input/Oresnik_statistika.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas.gaigr\Documents\Nucifraga\Data\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan.mikulas\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$387</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Y$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="630">
   <si>
     <t>ID</t>
   </si>
@@ -1904,10 +1904,25 @@
     <t>Spontanne_2</t>
   </si>
   <si>
-    <t>Provokovane_2</t>
-  </si>
-  <si>
     <t>Termin_2</t>
+  </si>
+  <si>
+    <t>DELKA_LINII</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>NO DATA</t>
+  </si>
+  <si>
+    <t>Hlasitost</t>
+  </si>
+  <si>
+    <t>Provokovano_2</t>
   </si>
 </sst>
 </file>
@@ -2382,27 +2397,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:U387"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Y387"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.26953125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="8.81640625" style="1"/>
-    <col min="8" max="8" width="9.1796875" style="1"/>
-    <col min="9" max="9" width="11.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.26953125" customWidth="1"/>
-    <col min="11" max="11" width="23.7265625" style="22" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.81640625" style="2"/>
-    <col min="16" max="16" width="9.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="1" customWidth="1"/>
+    <col min="6" max="7" width="8.85546875" style="1"/>
+    <col min="8" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" customWidth="1"/>
+    <col min="11" max="11" width="23.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.85546875" style="2"/>
+    <col min="16" max="16" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="21" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.81640625" style="2"/>
-    <col min="21" max="21" width="28.7265625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.85546875" style="2"/>
+    <col min="21" max="21" width="28.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -2458,16 +2472,28 @@
         <v>622</v>
       </c>
       <c r="S1" s="16" t="s">
+        <v>629</v>
+      </c>
+      <c r="T1" s="19" t="s">
         <v>623</v>
-      </c>
-      <c r="T1" s="19" t="s">
-        <v>624</v>
       </c>
       <c r="U1" s="20" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V1" t="s">
+        <v>628</v>
+      </c>
+      <c r="W1" t="s">
+        <v>624</v>
+      </c>
+      <c r="X1" t="s">
+        <v>625</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>2090</v>
       </c>
@@ -2531,8 +2557,20 @@
       <c r="U2" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V2">
+        <v>81</v>
+      </c>
+      <c r="W2">
+        <v>2</v>
+      </c>
+      <c r="X2">
+        <v>-949098.74862606998</v>
+      </c>
+      <c r="Y2">
+        <v>-731692.34058401699</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>201</v>
       </c>
@@ -2596,8 +2634,20 @@
       <c r="U3" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V3">
+        <v>81</v>
+      </c>
+      <c r="W3">
+        <v>2</v>
+      </c>
+      <c r="X3">
+        <v>-950291.69528856198</v>
+      </c>
+      <c r="Y3">
+        <v>-722986.90563551604</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>1836</v>
       </c>
@@ -2661,8 +2711,20 @@
       <c r="U4" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V4">
+        <v>81</v>
+      </c>
+      <c r="W4">
+        <v>3.9</v>
+      </c>
+      <c r="X4">
+        <v>-959903.50978095597</v>
+      </c>
+      <c r="Y4">
+        <v>-671058.97284480999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -2726,8 +2788,20 @@
       <c r="U5" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V5">
+        <v>89.5</v>
+      </c>
+      <c r="W5">
+        <v>4</v>
+      </c>
+      <c r="X5">
+        <v>-960026.28648242797</v>
+      </c>
+      <c r="Y5">
+        <v>-753950.18079041794</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>930</v>
       </c>
@@ -2791,8 +2865,20 @@
       <c r="U6" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V6">
+        <v>81</v>
+      </c>
+      <c r="W6">
+        <v>2.1</v>
+      </c>
+      <c r="X6">
+        <v>-955008.77339226403</v>
+      </c>
+      <c r="Y6">
+        <v>-729547.51332022296</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>874</v>
       </c>
@@ -2856,8 +2942,20 @@
       <c r="U7" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V7">
+        <v>81</v>
+      </c>
+      <c r="W7">
+        <v>1.7</v>
+      </c>
+      <c r="X7">
+        <v>-959347.63258397998</v>
+      </c>
+      <c r="Y7">
+        <v>-718298.82849324599</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>846</v>
       </c>
@@ -2921,8 +3019,20 @@
       <c r="U8" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V8">
+        <v>81</v>
+      </c>
+      <c r="W8">
+        <v>2</v>
+      </c>
+      <c r="X8">
+        <v>-961710.14492411399</v>
+      </c>
+      <c r="Y8">
+        <v>-721579.72385570605</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>600</v>
       </c>
@@ -2986,8 +3096,20 @@
       <c r="U9" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V9">
+        <v>81</v>
+      </c>
+      <c r="W9">
+        <v>2</v>
+      </c>
+      <c r="X9">
+        <v>-962495.86318871297</v>
+      </c>
+      <c r="Y9">
+        <v>-715762.19715450995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>813</v>
       </c>
@@ -3051,8 +3173,20 @@
       <c r="U10" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V10">
+        <v>81</v>
+      </c>
+      <c r="W10">
+        <v>2</v>
+      </c>
+      <c r="X10">
+        <v>-964859.96583290002</v>
+      </c>
+      <c r="Y10">
+        <v>-719043.32737415598</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>755</v>
       </c>
@@ -3116,8 +3250,20 @@
       <c r="U11" s="11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V11">
+        <v>85</v>
+      </c>
+      <c r="W11">
+        <v>5.2</v>
+      </c>
+      <c r="X11">
+        <v>-963568.75533568102</v>
+      </c>
+      <c r="Y11">
+        <v>-686305.61495679896</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>1713</v>
       </c>
@@ -3181,8 +3327,20 @@
       <c r="U12" s="11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V12">
+        <v>82</v>
+      </c>
+      <c r="W12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X12">
+        <v>-966701.52036391501</v>
+      </c>
+      <c r="Y12">
+        <v>-683749.63757737004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>920</v>
       </c>
@@ -3246,8 +3404,20 @@
       <c r="U13" s="11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V13">
+        <v>82</v>
+      </c>
+      <c r="W13">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X13">
+        <v>-969460.22172237199</v>
+      </c>
+      <c r="Y13">
+        <v>-684103.479798391</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>868</v>
       </c>
@@ -3311,8 +3481,20 @@
       <c r="U14" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V14">
+        <v>81</v>
+      </c>
+      <c r="W14">
+        <v>4.7</v>
+      </c>
+      <c r="X14">
+        <v>-965055.17359159596</v>
+      </c>
+      <c r="Y14">
+        <v>-674665.04814222001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>1822</v>
       </c>
@@ -3376,8 +3558,20 @@
       <c r="U15" s="11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V15">
+        <v>85</v>
+      </c>
+      <c r="W15">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X15">
+        <v>-970204.25921476702</v>
+      </c>
+      <c r="Y15">
+        <v>-678277.06418385298</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>909</v>
       </c>
@@ -3441,8 +3635,20 @@
       <c r="U16" s="11" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V16">
+        <v>82</v>
+      </c>
+      <c r="W16">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X16">
+        <v>-970941.82320725301</v>
+      </c>
+      <c r="Y16">
+        <v>-672449.77706960996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>925</v>
       </c>
@@ -3506,8 +3712,20 @@
       <c r="U17" s="11" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V17">
+        <v>91.5</v>
+      </c>
+      <c r="W17">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="X17">
+        <v>-968912.98045913596</v>
+      </c>
+      <c r="Y17">
+        <v>-666276.97910725395</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>1199</v>
       </c>
@@ -3571,8 +3789,20 @@
       <c r="U18" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V18">
+        <v>84.5</v>
+      </c>
+      <c r="W18">
+        <v>5.9</v>
+      </c>
+      <c r="X18">
+        <v>-967253.11625778605</v>
+      </c>
+      <c r="Y18">
+        <v>-781725.96881239105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>847</v>
       </c>
@@ -3636,8 +3866,20 @@
       <c r="U19" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V19">
+        <v>87</v>
+      </c>
+      <c r="W19">
+        <v>3.9</v>
+      </c>
+      <c r="X19">
+        <v>-968106.034949566</v>
+      </c>
+      <c r="Y19">
+        <v>-775902.55383568001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>845</v>
       </c>
@@ -3701,8 +3943,20 @@
       <c r="U20" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V20">
+        <v>81</v>
+      </c>
+      <c r="W20">
+        <v>2.1</v>
+      </c>
+      <c r="X20">
+        <v>-967221.98424905597</v>
+      </c>
+      <c r="Y20">
+        <v>-722327.30350880895</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>866</v>
       </c>
@@ -3766,8 +4020,20 @@
       <c r="U21" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V21">
+        <v>81</v>
+      </c>
+      <c r="W21">
+        <v>2</v>
+      </c>
+      <c r="X21">
+        <v>-969562.28554312105</v>
+      </c>
+      <c r="Y21">
+        <v>-704853.56990620203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>1816</v>
       </c>
@@ -3831,8 +4097,20 @@
       <c r="U22" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V22">
+        <v>81</v>
+      </c>
+      <c r="W22">
+        <v>5.4</v>
+      </c>
+      <c r="X22">
+        <v>-970329.41695958003</v>
+      </c>
+      <c r="Y22">
+        <v>-699027.184519317</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>1316</v>
       </c>
@@ -3896,8 +4174,20 @@
       <c r="U23" s="11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V23">
+        <v>85</v>
+      </c>
+      <c r="W23">
+        <v>5</v>
+      </c>
+      <c r="X23">
+        <v>-973848.07811578305</v>
+      </c>
+      <c r="Y23">
+        <v>-693558.36048157595</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>927</v>
       </c>
@@ -3961,8 +4251,20 @@
       <c r="U24" s="11" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V24">
+        <v>91.5</v>
+      </c>
+      <c r="W24">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X24">
+        <v>-976606.05851740297</v>
+      </c>
+      <c r="Y24">
+        <v>-693916.82003151998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>890</v>
       </c>
@@ -4026,8 +4328,20 @@
       <c r="U25" s="11" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V25">
+        <v>91.5</v>
+      </c>
+      <c r="W25">
+        <v>3.9</v>
+      </c>
+      <c r="X25">
+        <v>-972591.92597959703</v>
+      </c>
+      <c r="Y25">
+        <v>-681542.69700419495</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>1821</v>
       </c>
@@ -4091,8 +4405,20 @@
       <c r="U26" s="11" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V26">
+        <v>82</v>
+      </c>
+      <c r="W26">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X26">
+        <v>-978481.40894345101</v>
+      </c>
+      <c r="Y26">
+        <v>-679329.43138943403</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>908</v>
       </c>
@@ -4156,8 +4482,20 @@
       <c r="U27" s="11" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V27">
+        <v>82</v>
+      </c>
+      <c r="W27">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X27">
+        <v>-981979.59679483401</v>
+      </c>
+      <c r="Y27">
+        <v>-673840.68649721297</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>924</v>
       </c>
@@ -4221,8 +4559,20 @@
       <c r="U28" s="11" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V28">
+        <v>82</v>
+      </c>
+      <c r="W28">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X28">
+        <v>-977192.68114641996</v>
+      </c>
+      <c r="Y28">
+        <v>-667310.94048475299</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>938</v>
       </c>
@@ -4286,8 +4636,20 @@
       <c r="U29" s="11" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V29">
+        <v>82</v>
+      </c>
+      <c r="W29">
+        <v>6</v>
+      </c>
+      <c r="X29">
+        <v>-979952.51419882895</v>
+      </c>
+      <c r="Y29">
+        <v>-667655.60707653197</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>1373</v>
       </c>
@@ -4351,8 +4713,20 @@
       <c r="U30" s="11" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V30" t="s">
+        <v>627</v>
+      </c>
+      <c r="W30">
+        <v>6</v>
+      </c>
+      <c r="X30">
+        <v>-980316.23967459402</v>
+      </c>
+      <c r="Y30">
+        <v>-664736.61460538604</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>1859</v>
       </c>
@@ -4416,8 +4790,20 @@
       <c r="U31" s="11" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V31" t="s">
+        <v>627</v>
+      </c>
+      <c r="W31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X31">
+        <v>-978637.06297842599</v>
+      </c>
+      <c r="Y31">
+        <v>-655639.82144307205</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>837</v>
       </c>
@@ -4481,8 +4867,20 @@
       <c r="U32" s="11" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V32">
+        <v>89.5</v>
+      </c>
+      <c r="W32">
+        <v>5.9</v>
+      </c>
+      <c r="X32">
+        <v>-978994.111688509</v>
+      </c>
+      <c r="Y32">
+        <v>-652721.51294514502</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>836</v>
       </c>
@@ -4546,8 +4944,20 @@
       <c r="U33" s="11" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V33" t="s">
+        <v>627</v>
+      </c>
+      <c r="W33">
+        <v>4</v>
+      </c>
+      <c r="X33">
+        <v>-981754.94585353299</v>
+      </c>
+      <c r="Y33">
+        <v>-653058.522523319</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>705</v>
       </c>
@@ -4611,8 +5021,20 @@
       <c r="U34" s="11" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V34">
+        <v>89.5</v>
+      </c>
+      <c r="W34">
+        <v>5.9</v>
+      </c>
+      <c r="X34">
+        <v>-984515.74621249305</v>
+      </c>
+      <c r="Y34">
+        <v>-653395.53874583403</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>644</v>
       </c>
@@ -4676,8 +5098,20 @@
       <c r="U35" s="11" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V35">
+        <v>89.5</v>
+      </c>
+      <c r="W35">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X35">
+        <v>-983516.90027818095</v>
+      </c>
+      <c r="Y35">
+        <v>-638456.19738658902</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>1151</v>
       </c>
@@ -4741,8 +5175,20 @@
       <c r="U36" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V36">
+        <v>84.5</v>
+      </c>
+      <c r="W36">
+        <v>5.4</v>
+      </c>
+      <c r="X36">
+        <v>-974773.93170226202</v>
+      </c>
+      <c r="Y36">
+        <v>-806677.16400192201</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>1234</v>
       </c>
@@ -4806,8 +5252,20 @@
       <c r="U37" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V37">
+        <v>84.5</v>
+      </c>
+      <c r="W37">
+        <v>5.5</v>
+      </c>
+      <c r="X37">
+        <v>-968278.12123298796</v>
+      </c>
+      <c r="Y37">
+        <v>-793780.54298332799</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>788</v>
       </c>
@@ -4871,8 +5329,20 @@
       <c r="U38" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V38">
+        <v>87</v>
+      </c>
+      <c r="W38">
+        <v>3.8</v>
+      </c>
+      <c r="X38">
+        <v>-968712.141028304</v>
+      </c>
+      <c r="Y38">
+        <v>-790868.40525480697</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>24</v>
       </c>
@@ -4936,8 +5406,20 @@
       <c r="U39" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V39">
+        <v>87</v>
+      </c>
+      <c r="W39">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X39">
+        <v>-974213.30377500504</v>
+      </c>
+      <c r="Y39">
+        <v>-791686.72463091696</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>1173</v>
       </c>
@@ -5001,8 +5483,20 @@
       <c r="U40" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V40">
+        <v>84.5</v>
+      </c>
+      <c r="W40">
+        <v>5.8</v>
+      </c>
+      <c r="X40">
+        <v>-969575.29374736303</v>
+      </c>
+      <c r="Y40">
+        <v>-785043.38872094499</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>896</v>
       </c>
@@ -5066,8 +5560,20 @@
       <c r="U41" s="11" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V41">
+        <v>89.5</v>
+      </c>
+      <c r="W41">
+        <v>6.2</v>
+      </c>
+      <c r="X41">
+        <v>-987986.93914027303</v>
+      </c>
+      <c r="Y41">
+        <v>-647886.13212605205</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>743</v>
       </c>
@@ -5131,8 +5637,20 @@
       <c r="U42" s="11" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V42">
+        <v>89.5</v>
+      </c>
+      <c r="W42">
+        <v>6.2</v>
+      </c>
+      <c r="X42">
+        <v>-991452.40126167401</v>
+      </c>
+      <c r="Y42">
+        <v>-642369.77965099004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>835</v>
       </c>
@@ -5196,8 +5714,20 @@
       <c r="U43" s="11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V43">
+        <v>85.5</v>
+      </c>
+      <c r="W43">
+        <v>5.8</v>
+      </c>
+      <c r="X43">
+        <v>-989040.42664872005</v>
+      </c>
+      <c r="Y43">
+        <v>-639114.93287206197</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>1264</v>
       </c>
@@ -5261,8 +5791,20 @@
       <c r="U44" s="11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V44">
+        <v>85.5</v>
+      </c>
+      <c r="W44">
+        <v>4.8</v>
+      </c>
+      <c r="X44">
+        <v>-989388.34939495404</v>
+      </c>
+      <c r="Y44">
+        <v>-636190.78831606603</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>893</v>
       </c>
@@ -5326,8 +5868,20 @@
       <c r="U45" s="11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V45">
+        <v>85.5</v>
+      </c>
+      <c r="W45">
+        <v>6.7</v>
+      </c>
+      <c r="X45">
+        <v>-994563.81475001795</v>
+      </c>
+      <c r="Y45">
+        <v>-639773.69444348</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>1426</v>
       </c>
@@ -5391,8 +5945,20 @@
       <c r="U46" s="11" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V46" t="s">
+        <v>627</v>
+      </c>
+      <c r="W46">
+        <v>5.2</v>
+      </c>
+      <c r="X46">
+        <v>-992496.749307208</v>
+      </c>
+      <c r="Y46">
+        <v>-633592.75783905201</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>1683</v>
       </c>
@@ -5456,8 +6022,20 @@
       <c r="U47" s="11" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V47">
+        <v>81</v>
+      </c>
+      <c r="W47">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X47">
+        <v>-998965.42887454003</v>
+      </c>
+      <c r="Y47">
+        <v>-601704.37883975799</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>437</v>
       </c>
@@ -5521,8 +6099,20 @@
       <c r="U48" s="11" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V48">
+        <v>81</v>
+      </c>
+      <c r="W48">
+        <v>4.7</v>
+      </c>
+      <c r="X48">
+        <v>-999292.67627579602</v>
+      </c>
+      <c r="Y48">
+        <v>-598774.59010258096</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>831</v>
       </c>
@@ -5586,8 +6176,20 @@
       <c r="U49" s="11" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V49">
+        <v>84.5</v>
+      </c>
+      <c r="W49">
+        <v>5.2</v>
+      </c>
+      <c r="X49">
+        <v>-979829.27755166998</v>
+      </c>
+      <c r="Y49">
+        <v>-810429.46062645398</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>1218</v>
       </c>
@@ -5651,8 +6253,20 @@
       <c r="U50" s="11" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V50">
+        <v>85.5</v>
+      </c>
+      <c r="W50">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X50">
+        <v>-977964.77568458696</v>
+      </c>
+      <c r="Y50">
+        <v>-804176.72529241105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>1232</v>
       </c>
@@ -5716,8 +6330,20 @@
       <c r="U51" s="11" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V51">
+        <v>85.5</v>
+      </c>
+      <c r="W51">
+        <v>5.4</v>
+      </c>
+      <c r="X51">
+        <v>-979279.43389906106</v>
+      </c>
+      <c r="Y51">
+        <v>-795423.34067106305</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>1855</v>
       </c>
@@ -5781,8 +6407,20 @@
       <c r="U52" s="11" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V52">
+        <v>77</v>
+      </c>
+      <c r="W52">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X52">
+        <v>-997960.81694978802</v>
+      </c>
+      <c r="Y52">
+        <v>-658009.73662049999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>734</v>
       </c>
@@ -5846,8 +6484,20 @@
       <c r="U53" s="11" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V53">
+        <v>88.5</v>
+      </c>
+      <c r="W53">
+        <v>5.3</v>
+      </c>
+      <c r="X53">
+        <v>-1002498.13596505</v>
+      </c>
+      <c r="Y53">
+        <v>-643693.47029381397</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>483</v>
       </c>
@@ -5911,8 +6561,20 @@
       <c r="U54" s="11" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V54">
+        <v>88.5</v>
+      </c>
+      <c r="W54">
+        <v>4.3</v>
+      </c>
+      <c r="X54">
+        <v>-1008020.80933698</v>
+      </c>
+      <c r="Y54">
+        <v>-644355.34927919903</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>638</v>
       </c>
@@ -5976,8 +6638,20 @@
       <c r="U55" s="11" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V55">
+        <v>88.5</v>
+      </c>
+      <c r="W55">
+        <v>4.3</v>
+      </c>
+      <c r="X55">
+        <v>-1008371.70415946</v>
+      </c>
+      <c r="Y55">
+        <v>-641420.70199332898</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>1424</v>
       </c>
@@ -6041,8 +6715,20 @@
       <c r="U56" s="11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V56">
+        <v>85.5</v>
+      </c>
+      <c r="W56">
+        <v>6</v>
+      </c>
+      <c r="X56">
+        <v>-1000782.83311405</v>
+      </c>
+      <c r="Y56">
+        <v>-634571.75081756699</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>1422</v>
       </c>
@@ -6106,8 +6792,20 @@
       <c r="U57" s="11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V57">
+        <v>85.5</v>
+      </c>
+      <c r="W57">
+        <v>5.7</v>
+      </c>
+      <c r="X57">
+        <v>-1009068.61834565</v>
+      </c>
+      <c r="Y57">
+        <v>-635550.79652658396</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>1522</v>
       </c>
@@ -6171,8 +6869,20 @@
       <c r="U58" s="11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V58">
+        <v>85.5</v>
+      </c>
+      <c r="W58">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X58">
+        <v>-1009414.63755322</v>
+      </c>
+      <c r="Y58">
+        <v>-632615.54014378204</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>832</v>
       </c>
@@ -6230,8 +6940,20 @@
       <c r="U59" s="11" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V59">
+        <v>69.5</v>
+      </c>
+      <c r="W59">
+        <v>4.2</v>
+      </c>
+      <c r="X59">
+        <v>-1008693.43040321</v>
+      </c>
+      <c r="Y59">
+        <v>-614684.14656042005</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>884</v>
       </c>
@@ -6295,8 +7017,20 @@
       <c r="U60" s="11" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V60">
+        <v>81</v>
+      </c>
+      <c r="W60">
+        <v>5.4</v>
+      </c>
+      <c r="X60">
+        <v>-1012785.49717226</v>
+      </c>
+      <c r="Y60">
+        <v>-603252.03779666498</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>841</v>
       </c>
@@ -6360,8 +7094,20 @@
       <c r="U61" s="11" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V61">
+        <v>88.5</v>
+      </c>
+      <c r="W61">
+        <v>5</v>
+      </c>
+      <c r="X61">
+        <v>-1011133.18674989</v>
+      </c>
+      <c r="Y61">
+        <v>-641750.11980270001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>822</v>
       </c>
@@ -6425,8 +7171,20 @@
       <c r="U62" s="11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V62">
+        <v>85.5</v>
+      </c>
+      <c r="W62">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X62">
+        <v>-1015283.48628925</v>
+      </c>
+      <c r="Y62">
+        <v>-630326.69094945304</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>690</v>
       </c>
@@ -6490,8 +7248,20 @@
       <c r="U63" s="11" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V63">
+        <v>84.5</v>
+      </c>
+      <c r="W63">
+        <v>4.8</v>
+      </c>
+      <c r="X63">
+        <v>-1028297.3256747</v>
+      </c>
+      <c r="Y63">
+        <v>-563263.70053577295</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>724</v>
       </c>
@@ -6555,8 +7325,20 @@
       <c r="U64" s="11" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V64">
+        <v>85.5</v>
+      </c>
+      <c r="W64">
+        <v>6.4</v>
+      </c>
+      <c r="X64">
+        <v>-996271.30517460394</v>
+      </c>
+      <c r="Y64">
+        <v>-866935.17497308506</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>1097</v>
       </c>
@@ -6620,8 +7402,20 @@
       <c r="U65" s="11" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V65">
+        <v>85.5</v>
+      </c>
+      <c r="W65">
+        <v>7.7</v>
+      </c>
+      <c r="X65">
+        <v>-999015.922555984</v>
+      </c>
+      <c r="Y65">
+        <v>-867381.27187660895</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>901</v>
       </c>
@@ -6685,8 +7479,20 @@
       <c r="U66" s="11" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V66">
+        <v>89.5</v>
+      </c>
+      <c r="W66">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X66">
+        <v>-1034895.83612749</v>
+      </c>
+      <c r="Y66">
+        <v>-605728.59391638497</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>994</v>
       </c>
@@ -6750,8 +7556,20 @@
       <c r="U67" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V67">
+        <v>87</v>
+      </c>
+      <c r="W67">
+        <v>5.9</v>
+      </c>
+      <c r="X67">
+        <v>-999163.00787639199</v>
+      </c>
+      <c r="Y67">
+        <v>-900512.52526875294</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>1004</v>
       </c>
@@ -6815,8 +7633,20 @@
       <c r="U68" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V68">
+        <v>87</v>
+      </c>
+      <c r="W68">
+        <v>4.5</v>
+      </c>
+      <c r="X68">
+        <v>-1001904.84131301</v>
+      </c>
+      <c r="Y68">
+        <v>-900975.56225781795</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>1088</v>
       </c>
@@ -6880,8 +7710,20 @@
       <c r="U69" s="11" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V69">
+        <v>91</v>
+      </c>
+      <c r="W69">
+        <v>4.7</v>
+      </c>
+      <c r="X69">
+        <v>-999841.986429421</v>
+      </c>
+      <c r="Y69">
+        <v>-879548.252828756</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>718</v>
       </c>
@@ -6945,8 +7787,20 @@
       <c r="U70" s="11" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V70">
+        <v>91</v>
+      </c>
+      <c r="W70">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X70">
+        <v>-1002585.5940892</v>
+      </c>
+      <c r="Y70">
+        <v>-880000.50490271405</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>742</v>
       </c>
@@ -7010,8 +7864,20 @@
       <c r="U71" s="11" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V71">
+        <v>85.5</v>
+      </c>
+      <c r="W71">
+        <v>2.4</v>
+      </c>
+      <c r="X71">
+        <v>-1004027.71860792</v>
+      </c>
+      <c r="Y71">
+        <v>-871205.61463892402</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>733</v>
       </c>
@@ -7075,8 +7941,20 @@
       <c r="U72" s="11" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V72">
+        <v>85.5</v>
+      </c>
+      <c r="W72">
+        <v>5.4</v>
+      </c>
+      <c r="X72">
+        <v>-1001760.5321213501</v>
+      </c>
+      <c r="Y72">
+        <v>-867827.36472859804</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>1694</v>
       </c>
@@ -7140,8 +8018,20 @@
       <c r="U73" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V73">
+        <v>87</v>
+      </c>
+      <c r="W73">
+        <v>3.5</v>
+      </c>
+      <c r="X73">
+        <v>-1044274.20287414</v>
+      </c>
+      <c r="Y73">
+        <v>-621742.83824738802</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>906</v>
       </c>
@@ -7205,8 +8095,20 @@
       <c r="U74" s="11" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V74">
+        <v>89.5</v>
+      </c>
+      <c r="W74">
+        <v>5.8</v>
+      </c>
+      <c r="X74">
+        <v>-1041408.0784336</v>
+      </c>
+      <c r="Y74">
+        <v>-597489.13138538401</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>1598</v>
       </c>
@@ -7270,8 +8172,20 @@
       <c r="U75" s="11" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V75">
+        <v>89.5</v>
+      </c>
+      <c r="W75">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X75">
+        <v>-1041733.14183601</v>
+      </c>
+      <c r="Y75">
+        <v>-594535.86915040796</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>1875</v>
       </c>
@@ -7335,8 +8249,20 @@
       <c r="U76" s="11" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V76">
+        <v>79</v>
+      </c>
+      <c r="W76">
+        <v>4.2</v>
+      </c>
+      <c r="X76">
+        <v>-1046936.294808</v>
+      </c>
+      <c r="Y76">
+        <v>-598099.17837209103</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>907</v>
       </c>
@@ -7394,8 +8320,20 @@
       <c r="U77" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V77">
+        <v>87</v>
+      </c>
+      <c r="W77">
+        <v>4.2</v>
+      </c>
+      <c r="X77">
+        <v>-1044821.04928792</v>
+      </c>
+      <c r="Y77">
+        <v>-591884.38850296999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>886</v>
       </c>
@@ -7459,8 +8397,20 @@
       <c r="U78" s="11" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V78">
+        <v>84.5</v>
+      </c>
+      <c r="W78">
+        <v>5.6</v>
+      </c>
+      <c r="X78">
+        <v>-1050426.13490362</v>
+      </c>
+      <c r="Y78">
+        <v>-565569.54557326704</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>921</v>
       </c>
@@ -7524,8 +8474,20 @@
       <c r="U79" s="11" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V79">
+        <v>77</v>
+      </c>
+      <c r="W79">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X79">
+        <v>-1048879.60045279</v>
+      </c>
+      <c r="Y79">
+        <v>-553453.00636683404</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>553</v>
       </c>
@@ -7589,8 +8551,20 @@
       <c r="U80" s="11" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V80">
+        <v>63.5</v>
+      </c>
+      <c r="W80">
+        <v>6</v>
+      </c>
+      <c r="X80">
+        <v>-1047009.91428885</v>
+      </c>
+      <c r="Y80">
+        <v>-544302.36303887703</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>290</v>
       </c>
@@ -7654,8 +8628,20 @@
       <c r="U81" s="11" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="82" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V81">
+        <v>63.5</v>
+      </c>
+      <c r="W81">
+        <v>5.7</v>
+      </c>
+      <c r="X81">
+        <v>-1050072.9896299001</v>
+      </c>
+      <c r="Y81">
+        <v>-541621.904300906</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>864</v>
       </c>
@@ -7719,8 +8705,20 @@
       <c r="U82" s="11" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V82">
+        <v>63.5</v>
+      </c>
+      <c r="W82">
+        <v>5.3</v>
+      </c>
+      <c r="X82">
+        <v>-1050367.26587652</v>
+      </c>
+      <c r="Y82">
+        <v>-538663.69624806405</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>2044</v>
       </c>
@@ -7784,8 +8782,20 @@
       <c r="U83" s="11" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V83">
+        <v>63.5</v>
+      </c>
+      <c r="W83">
+        <v>5.2</v>
+      </c>
+      <c r="X83">
+        <v>-1053134.7245040201</v>
+      </c>
+      <c r="Y83">
+        <v>-538938.23188830004</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>953</v>
       </c>
@@ -7849,8 +8859,20 @@
       <c r="U84" s="11" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V84">
+        <v>91</v>
+      </c>
+      <c r="W84">
+        <v>4.5</v>
+      </c>
+      <c r="X84">
+        <v>-1013860.80220501</v>
+      </c>
+      <c r="Y84">
+        <v>-896953.01340189204</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>695</v>
       </c>
@@ -7914,8 +8936,20 @@
       <c r="U85" s="11" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V85">
+        <v>101.5</v>
+      </c>
+      <c r="W85">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X85">
+        <v>-1020126.16688157</v>
+      </c>
+      <c r="Y85">
+        <v>-858741.76323820697</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>815</v>
       </c>
@@ -7979,8 +9013,20 @@
       <c r="U86" s="11" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V86">
+        <v>101.5</v>
+      </c>
+      <c r="W86">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X86">
+        <v>-1024278.70806073</v>
+      </c>
+      <c r="Y86">
+        <v>-850352.76255174004</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>804</v>
       </c>
@@ -8044,8 +9090,20 @@
       <c r="U87" s="11" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V87">
+        <v>78</v>
+      </c>
+      <c r="W87">
+        <v>8.9</v>
+      </c>
+      <c r="X87">
+        <v>-1028640.67575109</v>
+      </c>
+      <c r="Y87">
+        <v>-784735.04009630298</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>803</v>
       </c>
@@ -8109,8 +9167,20 @@
       <c r="U88" s="11" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V88">
+        <v>68</v>
+      </c>
+      <c r="W88" t="s">
+        <v>627</v>
+      </c>
+      <c r="X88">
+        <v>-1034143.45292598</v>
+      </c>
+      <c r="Y88">
+        <v>-785537.98593761201</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>826</v>
       </c>
@@ -8168,8 +9238,20 @@
       <c r="U89" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V89">
+        <v>87</v>
+      </c>
+      <c r="W89">
+        <v>5.7</v>
+      </c>
+      <c r="X89">
+        <v>-1056201.3225920899</v>
+      </c>
+      <c r="Y89">
+        <v>-590131.04277847696</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>844</v>
       </c>
@@ -8233,8 +9315,20 @@
       <c r="U90" s="11" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V90">
+        <v>84.5</v>
+      </c>
+      <c r="W90">
+        <v>5.9</v>
+      </c>
+      <c r="X90">
+        <v>-1055648.5690733499</v>
+      </c>
+      <c r="Y90">
+        <v>-569107.25705609401</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>903</v>
       </c>
@@ -8298,8 +9392,20 @@
       <c r="U91" s="11" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V91">
+        <v>84.5</v>
+      </c>
+      <c r="W91">
+        <v>5.5</v>
+      </c>
+      <c r="X91">
+        <v>-1054110.1145808899</v>
+      </c>
+      <c r="Y91">
+        <v>-556977.70190774195</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>819</v>
       </c>
@@ -8363,8 +9469,20 @@
       <c r="U92" s="11" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V92">
+        <v>84.5</v>
+      </c>
+      <c r="W92">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X92">
+        <v>-1057480.7254355799</v>
+      </c>
+      <c r="Y92">
+        <v>-551337.39302897896</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>863</v>
       </c>
@@ -8428,8 +9546,20 @@
       <c r="U93" s="11" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V93">
+        <v>76</v>
+      </c>
+      <c r="W93">
+        <v>5</v>
+      </c>
+      <c r="X93">
+        <v>-1064204.2237978701</v>
+      </c>
+      <c r="Y93">
+        <v>-540036.4243064</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>869</v>
       </c>
@@ -8493,8 +9623,20 @@
       <c r="U94" s="11" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V94">
+        <v>76</v>
+      </c>
+      <c r="W94">
+        <v>5.3</v>
+      </c>
+      <c r="X94">
+        <v>-1059254.16418233</v>
+      </c>
+      <c r="Y94">
+        <v>-533561.25262528495</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>1107</v>
       </c>
@@ -8558,8 +9700,20 @@
       <c r="U95" s="11" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V95" t="s">
+        <v>627</v>
+      </c>
+      <c r="W95">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X95">
+        <v>-1023238.04646659</v>
+      </c>
+      <c r="Y95">
+        <v>-874338.89618242299</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>1106</v>
       </c>
@@ -8617,8 +9771,20 @@
       <c r="U96" s="11" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V96">
+        <v>70</v>
+      </c>
+      <c r="W96">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X96">
+        <v>-1025982.36147729</v>
+      </c>
+      <c r="Y96">
+        <v>-874786.48794853804</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>798</v>
       </c>
@@ -8682,8 +9848,20 @@
       <c r="U97" s="11" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V97">
+        <v>101.5</v>
+      </c>
+      <c r="W97">
+        <v>5</v>
+      </c>
+      <c r="X97">
+        <v>-1028833.92036719</v>
+      </c>
+      <c r="Y97">
+        <v>-857115.67637278698</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>701</v>
       </c>
@@ -8747,8 +9925,20 @@
       <c r="U98" s="11" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V98">
+        <v>101.5</v>
+      </c>
+      <c r="W98">
+        <v>5.6</v>
+      </c>
+      <c r="X98">
+        <v>-1030160.61758373</v>
+      </c>
+      <c r="Y98">
+        <v>-866395.22648511396</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
         <v>1130</v>
       </c>
@@ -8812,8 +10002,20 @@
       <c r="U99" s="11" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V99">
+        <v>91</v>
+      </c>
+      <c r="W99">
+        <v>5.5</v>
+      </c>
+      <c r="X99">
+        <v>-1034358.77888544</v>
+      </c>
+      <c r="Y99">
+        <v>-821746.25650259503</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
         <v>728</v>
       </c>
@@ -8877,8 +10079,20 @@
       <c r="U100" s="11" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V100">
+        <v>91</v>
+      </c>
+      <c r="W100">
+        <v>5.6</v>
+      </c>
+      <c r="X100">
+        <v>-1034808.46125979</v>
+      </c>
+      <c r="Y100">
+        <v>-818797.16480930406</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
         <v>1187</v>
       </c>
@@ -8942,8 +10156,20 @@
       <c r="U101" s="11" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V101">
+        <v>89</v>
+      </c>
+      <c r="W101">
+        <v>5.8</v>
+      </c>
+      <c r="X101">
+        <v>-1036590.70537143</v>
+      </c>
+      <c r="Y101">
+        <v>-806998.31968169403</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
         <v>395</v>
       </c>
@@ -9007,8 +10233,20 @@
       <c r="U102" s="11" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V102">
+        <v>75</v>
+      </c>
+      <c r="W102">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X102">
+        <v>-1063951.8100705401</v>
+      </c>
+      <c r="Y102">
+        <v>-620998.129550379</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>900</v>
       </c>
@@ -9072,8 +10310,20 @@
       <c r="U103" s="11" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V103">
+        <v>75</v>
+      </c>
+      <c r="W103">
+        <v>4.8</v>
+      </c>
+      <c r="X103">
+        <v>-1065294.4068262801</v>
+      </c>
+      <c r="Y103">
+        <v>-609134.31724822498</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>380</v>
       </c>
@@ -9137,8 +10387,20 @@
       <c r="U104" s="11" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V104">
+        <v>75</v>
+      </c>
+      <c r="W104">
+        <v>5.6</v>
+      </c>
+      <c r="X104">
+        <v>-1060098.83969731</v>
+      </c>
+      <c r="Y104">
+        <v>-605551.68670802203</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
         <v>807</v>
       </c>
@@ -9202,8 +10464,20 @@
       <c r="U105" s="11" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V105">
+        <v>87</v>
+      </c>
+      <c r="W105">
+        <v>4.2</v>
+      </c>
+      <c r="X105">
+        <v>-1064816.2985761601</v>
+      </c>
+      <c r="Y105">
+        <v>-588066.41893768997</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
         <v>1547</v>
       </c>
@@ -9267,8 +10541,20 @@
       <c r="U106" s="11" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V106">
+        <v>87</v>
+      </c>
+      <c r="W106">
+        <v>4.5</v>
+      </c>
+      <c r="X106">
+        <v>-1065454.50256958</v>
+      </c>
+      <c r="Y106">
+        <v>-582133.81533120398</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
         <v>824</v>
       </c>
@@ -9332,8 +10618,20 @@
       <c r="U107" s="11" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V107">
+        <v>87</v>
+      </c>
+      <c r="W107">
+        <v>5.8</v>
+      </c>
+      <c r="X107">
+        <v>-1069164.97674789</v>
+      </c>
+      <c r="Y107">
+        <v>-573524.869665595</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
         <v>843</v>
       </c>
@@ -9397,8 +10695,20 @@
       <c r="U108" s="11" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V108">
+        <v>87</v>
+      </c>
+      <c r="W108">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X108">
+        <v>-1066711.2802482799</v>
+      </c>
+      <c r="Y108">
+        <v>-570266.42576388898</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
         <v>852</v>
       </c>
@@ -9462,8 +10772,20 @@
       <c r="U109" s="11" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V109">
+        <v>78</v>
+      </c>
+      <c r="W109">
+        <v>9.9700000000000006</v>
+      </c>
+      <c r="X109">
+        <v>-1069443.38366035</v>
+      </c>
+      <c r="Y109">
+        <v>-543554.41593492695</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
         <v>862</v>
       </c>
@@ -9527,8 +10849,20 @@
       <c r="U110" s="11" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V110">
+        <v>78</v>
+      </c>
+      <c r="W110">
+        <v>7.39</v>
+      </c>
+      <c r="X110">
+        <v>-1072506.0108451699</v>
+      </c>
+      <c r="Y110">
+        <v>-540860.11537665804</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
         <v>825</v>
       </c>
@@ -9592,8 +10926,20 @@
       <c r="U111" s="11" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V111">
+        <v>78</v>
+      </c>
+      <c r="W111">
+        <v>6.21</v>
+      </c>
+      <c r="X111">
+        <v>-1067847.43066608</v>
+      </c>
+      <c r="Y111">
+        <v>-531407.92778933805</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
         <v>715</v>
       </c>
@@ -9657,8 +11003,20 @@
       <c r="U112" s="11" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V112">
+        <v>86.5</v>
+      </c>
+      <c r="W112">
+        <v>5</v>
+      </c>
+      <c r="X112">
+        <v>-1036477.57113039</v>
+      </c>
+      <c r="Y112">
+        <v>-879527.17327422497</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
         <v>730</v>
       </c>
@@ -9722,8 +11080,20 @@
       <c r="U113" s="11" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V113">
+        <v>86.5</v>
+      </c>
+      <c r="W113">
+        <v>5</v>
+      </c>
+      <c r="X113">
+        <v>-1037439.9617757</v>
+      </c>
+      <c r="Y113">
+        <v>-873626.16146565496</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>1060</v>
       </c>
@@ -9787,8 +11157,20 @@
       <c r="U114" s="11" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V114">
+        <v>86.5</v>
+      </c>
+      <c r="W114">
+        <v>5</v>
+      </c>
+      <c r="X114">
+        <v>-1039221.6292915799</v>
+      </c>
+      <c r="Y114">
+        <v>-879976.27534901397</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>194</v>
       </c>
@@ -9852,8 +11234,20 @@
       <c r="U115" s="11" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V115">
+        <v>81</v>
+      </c>
+      <c r="W115">
+        <v>5.2</v>
+      </c>
+      <c r="X115">
+        <v>-1039816.9864151001</v>
+      </c>
+      <c r="Y115">
+        <v>-858869.05419346201</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
         <v>266</v>
       </c>
@@ -9917,8 +11311,20 @@
       <c r="U116" s="11" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V116">
+        <v>81</v>
+      </c>
+      <c r="W116">
+        <v>5.7</v>
+      </c>
+      <c r="X116">
+        <v>-1038009.97839871</v>
+      </c>
+      <c r="Y116">
+        <v>-852529.13631094899</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
         <v>402</v>
       </c>
@@ -9982,8 +11388,20 @@
       <c r="U117" s="11" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V117">
+        <v>81</v>
+      </c>
+      <c r="W117">
+        <v>5.5</v>
+      </c>
+      <c r="X117">
+        <v>-1041223.35451041</v>
+      </c>
+      <c r="Y117">
+        <v>-850011.68246696598</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
         <v>265</v>
       </c>
@@ -10047,8 +11465,20 @@
       <c r="U118" s="11" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V118">
+        <v>81</v>
+      </c>
+      <c r="W118">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X118">
+        <v>-1043502.45549848</v>
+      </c>
+      <c r="Y118">
+        <v>-853399.65237637598</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
         <v>838</v>
       </c>
@@ -10112,8 +11542,20 @@
       <c r="U119" s="11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V119">
+        <v>85</v>
+      </c>
+      <c r="W119">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X119">
+        <v>-1049029.5418986201</v>
+      </c>
+      <c r="Y119">
+        <v>-836096.343571987</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="4">
         <v>1171</v>
       </c>
@@ -10177,8 +11619,20 @@
       <c r="U120" s="11" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V120">
+        <v>99</v>
+      </c>
+      <c r="W120">
+        <v>5</v>
+      </c>
+      <c r="X120">
+        <v>-1042604.59934944</v>
+      </c>
+      <c r="Y120">
+        <v>-823005.94178451004</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="4">
         <v>99</v>
       </c>
@@ -10242,8 +11696,20 @@
       <c r="U121" s="11" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V121">
+        <v>91</v>
+      </c>
+      <c r="W121">
+        <v>5.2</v>
+      </c>
+      <c r="X121">
+        <v>-1055721.2297844901</v>
+      </c>
+      <c r="Y121">
+        <v>-791710.67640571599</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
         <v>148</v>
       </c>
@@ -10307,8 +11773,20 @@
       <c r="U122" s="11" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V122">
+        <v>68</v>
+      </c>
+      <c r="W122">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X122">
+        <v>-1056154.12207951</v>
+      </c>
+      <c r="Y122">
+        <v>-788749.68417650799</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>329</v>
       </c>
@@ -10372,8 +11850,20 @@
       <c r="U123" s="11" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V123">
+        <v>89</v>
+      </c>
+      <c r="W123">
+        <v>5.4</v>
+      </c>
+      <c r="X123">
+        <v>-1056596.1510943801</v>
+      </c>
+      <c r="Y123">
+        <v>-725407.149769802</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="4">
         <v>816</v>
       </c>
@@ -10437,8 +11927,20 @@
       <c r="U124" s="11" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V124">
+        <v>89.5</v>
+      </c>
+      <c r="W124">
+        <v>4.5</v>
+      </c>
+      <c r="X124">
+        <v>-1056992.1263413201</v>
+      </c>
+      <c r="Y124">
+        <v>-722445.68521413906</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
         <v>474</v>
       </c>
@@ -10502,8 +12004,20 @@
       <c r="U125" s="11" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V125">
+        <v>89.5</v>
+      </c>
+      <c r="W125">
+        <v>4.8</v>
+      </c>
+      <c r="X125">
+        <v>-1059748.1580073501</v>
+      </c>
+      <c r="Y125">
+        <v>-722813.41329258902</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="4">
         <v>2152</v>
       </c>
@@ -10567,8 +12081,20 @@
       <c r="U126" s="11" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V126">
+        <v>89.5</v>
+      </c>
+      <c r="W126">
+        <v>4.5</v>
+      </c>
+      <c r="X126">
+        <v>-1057386.4560136001</v>
+      </c>
+      <c r="Y126">
+        <v>-719483.99938661396</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="4">
         <v>2151</v>
       </c>
@@ -10632,8 +12158,20 @@
       <c r="U127" s="11" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V127">
+        <v>89.5</v>
+      </c>
+      <c r="W127">
+        <v>5</v>
+      </c>
+      <c r="X127">
+        <v>-1060142.6929515901</v>
+      </c>
+      <c r="Y127">
+        <v>-719850.19587845996</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="4">
         <v>1693</v>
       </c>
@@ -10697,8 +12235,20 @@
       <c r="U128" s="11" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V128">
+        <v>81</v>
+      </c>
+      <c r="W128">
+        <v>5.5</v>
+      </c>
+      <c r="X128">
+        <v>-1060926.8232917699</v>
+      </c>
+      <c r="Y128">
+        <v>-713923.10095244006</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="4">
         <v>1692</v>
       </c>
@@ -10762,8 +12312,20 @@
       <c r="U129" s="11" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V129">
+        <v>81</v>
+      </c>
+      <c r="W129">
+        <v>4.5</v>
+      </c>
+      <c r="X129">
+        <v>-1066440.0683216399</v>
+      </c>
+      <c r="Y129">
+        <v>-714649.36775136099</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="4">
         <v>1268</v>
       </c>
@@ -10827,8 +12389,20 @@
       <c r="U130" s="11" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V130">
+        <v>75</v>
+      </c>
+      <c r="W130">
+        <v>4</v>
+      </c>
+      <c r="X130">
+        <v>-1072578.2801315</v>
+      </c>
+      <c r="Y130">
+        <v>-618975.09947607096</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="4">
         <v>1582</v>
       </c>
@@ -10892,8 +12466,20 @@
       <c r="U131" s="11" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V131">
+        <v>93</v>
+      </c>
+      <c r="W131">
+        <v>4.3</v>
+      </c>
+      <c r="X131">
+        <v>-1080756.64025101</v>
+      </c>
+      <c r="Y131">
+        <v>-595810.32494818605</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="4">
         <v>1911</v>
       </c>
@@ -10957,8 +12543,20 @@
       <c r="U132" s="11" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V132">
+        <v>93</v>
+      </c>
+      <c r="W132">
+        <v>4.5</v>
+      </c>
+      <c r="X132">
+        <v>-1081080.8648469399</v>
+      </c>
+      <c r="Y132">
+        <v>-592835.33285919495</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" s="4">
         <v>773</v>
       </c>
@@ -11022,8 +12620,20 @@
       <c r="U133" s="11" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V133">
+        <v>93</v>
+      </c>
+      <c r="W133">
+        <v>4.7</v>
+      </c>
+      <c r="X133">
+        <v>-1078959.7608211201</v>
+      </c>
+      <c r="Y133">
+        <v>-586587.35920765798</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
         <v>2019</v>
       </c>
@@ -11087,8 +12697,20 @@
       <c r="U134" s="11" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V134">
+        <v>87</v>
+      </c>
+      <c r="W134">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X134">
+        <v>-1082677.37534892</v>
+      </c>
+      <c r="Y134">
+        <v>-577957.62900731398</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
         <v>428</v>
       </c>
@@ -11152,8 +12774,20 @@
       <c r="U135" s="11" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V135">
+        <v>93.5</v>
+      </c>
+      <c r="W135">
+        <v>5</v>
+      </c>
+      <c r="X135">
+        <v>-1077447.00196115</v>
+      </c>
+      <c r="Y135">
+        <v>-547355.96405750501</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
         <v>2037</v>
       </c>
@@ -11217,8 +12851,20 @@
       <c r="U136" s="11" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V136">
+        <v>93.5</v>
+      </c>
+      <c r="W136">
+        <v>5.5</v>
+      </c>
+      <c r="X136">
+        <v>-1078040.3827214299</v>
+      </c>
+      <c r="Y136">
+        <v>-541409.26186496695</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
         <v>1099</v>
       </c>
@@ -11282,8 +12928,20 @@
       <c r="U137" s="11" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V137">
+        <v>86.5</v>
+      </c>
+      <c r="W137">
+        <v>5</v>
+      </c>
+      <c r="X137">
+        <v>-1045673.60043913</v>
+      </c>
+      <c r="Y137">
+        <v>-874964.21512575704</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
         <v>721</v>
       </c>
@@ -11347,8 +13005,20 @@
       <c r="U138" s="11" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V138">
+        <v>86.5</v>
+      </c>
+      <c r="W138">
+        <v>5</v>
+      </c>
+      <c r="X138">
+        <v>-1048418.14475124</v>
+      </c>
+      <c r="Y138">
+        <v>-875410.22050987999</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
         <v>821</v>
       </c>
@@ -11412,8 +13082,20 @@
       <c r="U139" s="11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V139">
+        <v>85</v>
+      </c>
+      <c r="W139">
+        <v>4.7</v>
+      </c>
+      <c r="X139">
+        <v>-1056350.73216744</v>
+      </c>
+      <c r="Y139">
+        <v>-843297.481329559</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
         <v>722</v>
       </c>
@@ -11477,8 +13159,20 @@
       <c r="U140" s="11" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V140">
+        <v>99</v>
+      </c>
+      <c r="W140">
+        <v>6</v>
+      </c>
+      <c r="X140">
+        <v>-1056799.03843816</v>
+      </c>
+      <c r="Y140">
+        <v>-822143.95399014198</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
         <v>792</v>
       </c>
@@ -11542,8 +13236,20 @@
       <c r="U141" s="11" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V141">
+        <v>99</v>
+      </c>
+      <c r="W141">
+        <v>5.6</v>
+      </c>
+      <c r="X141">
+        <v>-1065852.93896936</v>
+      </c>
+      <c r="Y141">
+        <v>-799256.13670838298</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A142" s="4">
         <v>4</v>
       </c>
@@ -11607,8 +13313,20 @@
       <c r="U142" s="11" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V142">
+        <v>85</v>
+      </c>
+      <c r="W142">
+        <v>4.5</v>
+      </c>
+      <c r="X142">
+        <v>-1068877.8175474501</v>
+      </c>
+      <c r="Y142">
+        <v>-778484.57150027296</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A143" s="4">
         <v>317</v>
       </c>
@@ -11672,8 +13390,20 @@
       <c r="U143" s="11" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V143">
+        <v>119</v>
+      </c>
+      <c r="W143">
+        <v>6.3</v>
+      </c>
+      <c r="X143">
+        <v>-1067816.9142231699</v>
+      </c>
+      <c r="Y143">
+        <v>-766220.74615105195</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
         <v>1249</v>
       </c>
@@ -11737,8 +13467,20 @@
       <c r="U144" s="11" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V144">
+        <v>119</v>
+      </c>
+      <c r="W144">
+        <v>6</v>
+      </c>
+      <c r="X144">
+        <v>-1070149.38071526</v>
+      </c>
+      <c r="Y144">
+        <v>-769578.93055814598</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
         <v>1370</v>
       </c>
@@ -11802,8 +13544,20 @@
       <c r="U145" s="11" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V145">
+        <v>89</v>
+      </c>
+      <c r="W145">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X145">
+        <v>-1065482.3560320199</v>
+      </c>
+      <c r="Y145">
+        <v>-762865.39360368205</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A146" s="4">
         <v>487</v>
       </c>
@@ -11867,8 +13621,20 @@
       <c r="U146" s="11" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V146">
+        <v>81</v>
+      </c>
+      <c r="W146">
+        <v>6</v>
+      </c>
+      <c r="X146">
+        <v>-1066419.0752892001</v>
+      </c>
+      <c r="Y146">
+        <v>-735785.62216368795</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A147" s="4">
         <v>1691</v>
       </c>
@@ -11932,8 +13698,20 @@
       <c r="U147" s="11" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V147">
+        <v>81</v>
+      </c>
+      <c r="W147">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X147">
+        <v>-1071953.2556237599</v>
+      </c>
+      <c r="Y147">
+        <v>-715375.63146352395</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
         <v>1803</v>
       </c>
@@ -11997,8 +13775,20 @@
       <c r="U148" s="11" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V148">
+        <v>81</v>
+      </c>
+      <c r="W148">
+        <v>5</v>
+      </c>
+      <c r="X148">
+        <v>-1078246.3582231901</v>
+      </c>
+      <c r="Y148">
+        <v>-710155.55292445305</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A149" s="4">
         <v>1295</v>
       </c>
@@ -12062,8 +13852,20 @@
       <c r="U149" s="11" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V149">
+        <v>86.5</v>
+      </c>
+      <c r="W149">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X149">
+        <v>-1076646.37329711</v>
+      </c>
+      <c r="Y149">
+        <v>-700878.94818071101</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A150" s="4">
         <v>681</v>
       </c>
@@ -12127,8 +13929,20 @@
       <c r="U150" s="11" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V150">
+        <v>86.5</v>
+      </c>
+      <c r="W150">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X150">
+        <v>-1077028.7339695201</v>
+      </c>
+      <c r="Y150">
+        <v>-697906.34035486204</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A151" s="4">
         <v>645</v>
       </c>
@@ -12192,8 +14006,20 @@
       <c r="U151" s="11" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V151">
+        <v>86.5</v>
+      </c>
+      <c r="W151">
+        <v>4</v>
+      </c>
+      <c r="X151">
+        <v>-1077409.4458332299</v>
+      </c>
+      <c r="Y151">
+        <v>-694933.51939692697</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A152" s="4">
         <v>1843</v>
       </c>
@@ -12257,8 +14083,20 @@
       <c r="U152" s="11" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V152">
+        <v>86.5</v>
+      </c>
+      <c r="W152">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X152">
+        <v>-1080924.2708455001</v>
+      </c>
+      <c r="Y152">
+        <v>-689336.60182528105</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A153" s="4">
         <v>855</v>
       </c>
@@ -12322,8 +14160,20 @@
       <c r="U153" s="11" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V153">
+        <v>93</v>
+      </c>
+      <c r="W153">
+        <v>5.6</v>
+      </c>
+      <c r="X153">
+        <v>-1085301.24654377</v>
+      </c>
+      <c r="Y153">
+        <v>-605347.37141388399</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A154" s="4">
         <v>905</v>
       </c>
@@ -12387,8 +14237,20 @@
       <c r="U154" s="11" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V154">
+        <v>93</v>
+      </c>
+      <c r="W154">
+        <v>4.5</v>
+      </c>
+      <c r="X154">
+        <v>-1085630.7430589199</v>
+      </c>
+      <c r="Y154">
+        <v>-602369.88577309903</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A155" s="4">
         <v>1909</v>
       </c>
@@ -12452,8 +14314,20 @@
       <c r="U155" s="11" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V155">
+        <v>93</v>
+      </c>
+      <c r="W155">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X155">
+        <v>-1092137.79064079</v>
+      </c>
+      <c r="Y155">
+        <v>-594037.30527693103</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
         <v>425</v>
       </c>
@@ -12517,8 +14391,20 @@
       <c r="U156" s="11" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V156">
+        <v>93.5</v>
+      </c>
+      <c r="W156">
+        <v>5</v>
+      </c>
+      <c r="X156">
+        <v>-1088514.1292904599</v>
+      </c>
+      <c r="Y156">
+        <v>-548466.48030042497</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A157" s="4">
         <v>902</v>
       </c>
@@ -12582,8 +14468,20 @@
       <c r="U157" s="11" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V157">
+        <v>93.5</v>
+      </c>
+      <c r="W157">
+        <v>4.5</v>
+      </c>
+      <c r="X157">
+        <v>-1093334.5163064499</v>
+      </c>
+      <c r="Y157">
+        <v>-527874.42489802605</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A158" s="4">
         <v>1087</v>
       </c>
@@ -12647,8 +14545,20 @@
       <c r="U158" s="11" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V158">
+        <v>86.5</v>
+      </c>
+      <c r="W158">
+        <v>5</v>
+      </c>
+      <c r="X158">
+        <v>-1057457.0999606899</v>
+      </c>
+      <c r="Y158">
+        <v>-889044.38337244606</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A159" s="4">
         <v>712</v>
       </c>
@@ -12712,8 +14622,20 @@
       <c r="U159" s="11" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V159">
+        <v>86.5</v>
+      </c>
+      <c r="W159">
+        <v>5</v>
+      </c>
+      <c r="X159">
+        <v>-1061174.09624425</v>
+      </c>
+      <c r="Y159">
+        <v>-883568.85243679199</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A160" s="4">
         <v>828</v>
       </c>
@@ -12777,8 +14699,20 @@
       <c r="U160" s="11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V160">
+        <v>85</v>
+      </c>
+      <c r="W160">
+        <v>5</v>
+      </c>
+      <c r="X160">
+        <v>-1059509.3652551</v>
+      </c>
+      <c r="Y160">
+        <v>-858974.28926963103</v>
+      </c>
+    </row>
+    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A161" s="4">
         <v>840</v>
       </c>
@@ -12842,8 +14776,20 @@
       <c r="U161" s="11" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V161">
+        <v>99</v>
+      </c>
+      <c r="W161">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X161">
+        <v>-1065045.4151798</v>
+      </c>
+      <c r="Y161">
+        <v>-823398.92968664598</v>
+      </c>
+    </row>
+    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A162" s="4">
         <v>160</v>
       </c>
@@ -12907,8 +14853,20 @@
       <c r="U162" s="11" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V162">
+        <v>99</v>
+      </c>
+      <c r="W162">
+        <v>5.6</v>
+      </c>
+      <c r="X162">
+        <v>-1068164.56753371</v>
+      </c>
+      <c r="Y162">
+        <v>-802630.12089051201</v>
+      </c>
+    </row>
+    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A163" s="4">
         <v>1244</v>
       </c>
@@ -12972,8 +14930,20 @@
       <c r="U163" s="11" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V163">
+        <v>99</v>
+      </c>
+      <c r="W163">
+        <v>6.2</v>
+      </c>
+      <c r="X163">
+        <v>-1071791.6613195899</v>
+      </c>
+      <c r="Y163">
+        <v>-797098.49171975604</v>
+      </c>
+    </row>
+    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A164" s="4">
         <v>791</v>
       </c>
@@ -13037,8 +15007,20 @@
       <c r="U164" s="11" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V164">
+        <v>79.5</v>
+      </c>
+      <c r="W164">
+        <v>4.5</v>
+      </c>
+      <c r="X164">
+        <v>-1077293.27342302</v>
+      </c>
+      <c r="Y164">
+        <v>-797907.48128791503</v>
+      </c>
+    </row>
+    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A165" s="4">
         <v>173</v>
       </c>
@@ -13102,8 +15084,20 @@
       <c r="U165" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V165">
+        <v>87</v>
+      </c>
+      <c r="W165">
+        <v>5.6</v>
+      </c>
+      <c r="X165">
+        <v>-1070773.5414176499</v>
+      </c>
+      <c r="Y165">
+        <v>-784818.86033042299</v>
+      </c>
+    </row>
+    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A166" s="4">
         <v>12</v>
       </c>
@@ -13167,8 +15161,20 @@
       <c r="U166" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V166">
+        <v>87</v>
+      </c>
+      <c r="W166">
+        <v>5.2</v>
+      </c>
+      <c r="X166">
+        <v>-1071202.5768912199</v>
+      </c>
+      <c r="Y166">
+        <v>-781849.48436061502</v>
+      </c>
+    </row>
+    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
         <v>801</v>
       </c>
@@ -13232,8 +15238,20 @@
       <c r="U167" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V167">
+        <v>87</v>
+      </c>
+      <c r="W167">
+        <v>5.3</v>
+      </c>
+      <c r="X167">
+        <v>-1079028.6108863601</v>
+      </c>
+      <c r="Y167">
+        <v>-786013.94361614599</v>
+      </c>
+    </row>
+    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A168" s="4">
         <v>842</v>
       </c>
@@ -13297,8 +15315,20 @@
       <c r="U168" s="11" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V168">
+        <v>119</v>
+      </c>
+      <c r="W168">
+        <v>5.4</v>
+      </c>
+      <c r="X168">
+        <v>-1072055.6830853799</v>
+      </c>
+      <c r="Y168">
+        <v>-775910.02588822402</v>
+      </c>
+    </row>
+    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A169" s="4">
         <v>762</v>
       </c>
@@ -13362,8 +15392,20 @@
       <c r="U169" s="11" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V169">
+        <v>119</v>
+      </c>
+      <c r="W169">
+        <v>5.6</v>
+      </c>
+      <c r="X169">
+        <v>-1072479.7544064899</v>
+      </c>
+      <c r="Y169">
+        <v>-772939.94560549594</v>
+      </c>
+    </row>
+    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A170" s="4">
         <v>460</v>
       </c>
@@ -13427,8 +15469,20 @@
       <c r="U170" s="11" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V170">
+        <v>81</v>
+      </c>
+      <c r="W170">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X170">
+        <v>-1087704.31452074</v>
+      </c>
+      <c r="Y170">
+        <v>-723512.10455776297</v>
+      </c>
+    </row>
+    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A171" s="4">
         <v>363</v>
       </c>
@@ -13492,8 +15546,20 @@
       <c r="U171" s="11" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V171">
+        <v>81</v>
+      </c>
+      <c r="W171">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X171">
+        <v>-1088099.23676791</v>
+      </c>
+      <c r="Y171">
+        <v>-720533.35800287302</v>
+      </c>
+    </row>
+    <row r="172" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A172" s="4">
         <v>861</v>
       </c>
@@ -13557,8 +15623,20 @@
       <c r="U172" s="11" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V172">
+        <v>86.5</v>
+      </c>
+      <c r="W172">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X172">
+        <v>-1084058.7586057601</v>
+      </c>
+      <c r="Y172">
+        <v>-686709.44753400201</v>
+      </c>
+    </row>
+    <row r="173" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A173" s="4">
         <v>1562</v>
       </c>
@@ -13622,8 +15700,20 @@
       <c r="U173" s="11" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V173">
+        <v>77</v>
+      </c>
+      <c r="W173">
+        <v>6.6</v>
+      </c>
+      <c r="X173">
+        <v>-1088087.6019836799</v>
+      </c>
+      <c r="Y173">
+        <v>-653954.16113631998</v>
+      </c>
+    </row>
+    <row r="174" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A174" s="4">
         <v>882</v>
       </c>
@@ -13687,8 +15777,20 @@
       <c r="U174" s="11" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V174">
+        <v>63.5</v>
+      </c>
+      <c r="W174">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X174">
+        <v>-1098486.1224017299</v>
+      </c>
+      <c r="Y174">
+        <v>-637042.92866738199</v>
+      </c>
+    </row>
+    <row r="175" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A175" s="4">
         <v>917</v>
       </c>
@@ -13752,8 +15854,20 @@
       <c r="U175" s="11" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V175">
+        <v>63.5</v>
+      </c>
+      <c r="W175">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X175">
+        <v>-1099522.2353736199</v>
+      </c>
+      <c r="Y175">
+        <v>-628088.14359593799</v>
+      </c>
+    </row>
+    <row r="176" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A176" s="4">
         <v>1978</v>
       </c>
@@ -13817,8 +15931,20 @@
       <c r="U176" s="11" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V176">
+        <v>93</v>
+      </c>
+      <c r="W176">
+        <v>5.2</v>
+      </c>
+      <c r="X176">
+        <v>-1093591.77616684</v>
+      </c>
+      <c r="Y176">
+        <v>-606267.15825011104</v>
+      </c>
+    </row>
+    <row r="177" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A177" s="4">
         <v>904</v>
       </c>
@@ -13882,8 +16008,20 @@
       <c r="U177" s="11" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V177">
+        <v>93</v>
+      </c>
+      <c r="W177">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X177">
+        <v>-1093921.7918386301</v>
+      </c>
+      <c r="Y177">
+        <v>-603285.09742890403</v>
+      </c>
+    </row>
+    <row r="178" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
         <v>415</v>
       </c>
@@ -13947,8 +16085,20 @@
       <c r="U178" s="11" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V178">
+        <v>69.5</v>
+      </c>
+      <c r="W178">
+        <v>5.6</v>
+      </c>
+      <c r="X178">
+        <v>-1096817.8984463401</v>
+      </c>
+      <c r="Y178">
+        <v>-576438.28624392406</v>
+      </c>
+    </row>
+    <row r="179" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A179" s="4">
         <v>899</v>
       </c>
@@ -14012,8 +16162,20 @@
       <c r="U179" s="11" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V179">
+        <v>93.5</v>
+      </c>
+      <c r="W179">
+        <v>4.5</v>
+      </c>
+      <c r="X179">
+        <v>-1104692.89099919</v>
+      </c>
+      <c r="Y179">
+        <v>-525954.24396956596</v>
+      </c>
+    </row>
+    <row r="180" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A180" s="4">
         <v>1070</v>
       </c>
@@ -14077,8 +16239,20 @@
       <c r="U180" s="11" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V180">
+        <v>86.5</v>
+      </c>
+      <c r="W180">
+        <v>5</v>
+      </c>
+      <c r="X180">
+        <v>-1072635.56089784</v>
+      </c>
+      <c r="Y180">
+        <v>-882394.59314669995</v>
+      </c>
+    </row>
+    <row r="181" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A181" s="4">
         <v>795</v>
       </c>
@@ -14142,8 +16316,20 @@
       <c r="U181" s="11" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V181">
+        <v>79.5</v>
+      </c>
+      <c r="W181">
+        <v>4.5</v>
+      </c>
+      <c r="X181">
+        <v>-1085982.6422132701</v>
+      </c>
+      <c r="Y181">
+        <v>-796143.30279111001</v>
+      </c>
+    </row>
+    <row r="182" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A182" s="4">
         <v>182</v>
       </c>
@@ -14207,8 +16393,20 @@
       <c r="U182" s="11" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="183" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V182">
+        <v>79.5</v>
+      </c>
+      <c r="W182">
+        <v>5</v>
+      </c>
+      <c r="X182">
+        <v>-1086417.96523461</v>
+      </c>
+      <c r="Y182">
+        <v>-793165.43564827705</v>
+      </c>
+    </row>
+    <row r="183" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A183" s="4">
         <v>800</v>
       </c>
@@ -14272,8 +16470,20 @@
       <c r="U183" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="184" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V183">
+        <v>87</v>
+      </c>
+      <c r="W183">
+        <v>5.3</v>
+      </c>
+      <c r="X183">
+        <v>-1081780.2896251699</v>
+      </c>
+      <c r="Y183">
+        <v>-786412.29646753694</v>
+      </c>
+    </row>
+    <row r="184" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A184" s="4">
         <v>1247</v>
       </c>
@@ -14337,8 +16547,20 @@
       <c r="U184" s="11" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V184">
+        <v>85</v>
+      </c>
+      <c r="W184">
+        <v>5.3</v>
+      </c>
+      <c r="X184">
+        <v>-1083913.25498781</v>
+      </c>
+      <c r="Y184">
+        <v>-771532.40305446601</v>
+      </c>
+    </row>
+    <row r="185" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A185" s="4">
         <v>1396</v>
       </c>
@@ -14402,8 +16624,20 @@
       <c r="U185" s="11" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V185">
+        <v>89</v>
+      </c>
+      <c r="W185">
+        <v>5.3</v>
+      </c>
+      <c r="X185">
+        <v>-1100690.72371037</v>
+      </c>
+      <c r="Y185">
+        <v>-710050.31189339899</v>
+      </c>
+    </row>
+    <row r="186" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A186" s="4">
         <v>466</v>
       </c>
@@ -14467,8 +16701,20 @@
       <c r="U186" s="11" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V186">
+        <v>89</v>
+      </c>
+      <c r="W186">
+        <v>4</v>
+      </c>
+      <c r="X186">
+        <v>-1101078.1693833601</v>
+      </c>
+      <c r="Y186">
+        <v>-707064.36506771599</v>
+      </c>
+    </row>
+    <row r="187" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A187" s="4">
         <v>682</v>
       </c>
@@ -14532,8 +16778,20 @@
       <c r="U187" s="11" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="188" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V187">
+        <v>89</v>
+      </c>
+      <c r="W187">
+        <v>5.2</v>
+      </c>
+      <c r="X187">
+        <v>-1099472.71645661</v>
+      </c>
+      <c r="Y187">
+        <v>-697752.83832536195</v>
+      </c>
+    </row>
+    <row r="188" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A188" s="4">
         <v>679</v>
       </c>
@@ -14597,8 +16855,20 @@
       <c r="U188" s="11" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V188">
+        <v>89</v>
+      </c>
+      <c r="W188">
+        <v>5.6</v>
+      </c>
+      <c r="X188">
+        <v>-1101848.0924519501</v>
+      </c>
+      <c r="Y188">
+        <v>-701091.831230385</v>
+      </c>
+    </row>
+    <row r="189" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
         <v>471</v>
       </c>
@@ -14662,8 +16932,20 @@
       <c r="U189" s="11" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V189">
+        <v>89.5</v>
+      </c>
+      <c r="W189">
+        <v>4.3</v>
+      </c>
+      <c r="X189">
+        <v>-1097474.0626278101</v>
+      </c>
+      <c r="Y189">
+        <v>-691432.741320548</v>
+      </c>
+    </row>
+    <row r="190" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A190" s="4">
         <v>934</v>
       </c>
@@ -14727,8 +17009,20 @@
       <c r="U190" s="11" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V190">
+        <v>89.5</v>
+      </c>
+      <c r="W190">
+        <v>5</v>
+      </c>
+      <c r="X190">
+        <v>-1100985.2971415501</v>
+      </c>
+      <c r="Y190">
+        <v>-685810.51175071695</v>
+      </c>
+    </row>
+    <row r="191" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A191" s="4">
         <v>879</v>
       </c>
@@ -14792,8 +17086,20 @@
       <c r="U191" s="11" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V191">
+        <v>63.5</v>
+      </c>
+      <c r="W191">
+        <v>5.9</v>
+      </c>
+      <c r="X191">
+        <v>-1102603.3656333401</v>
+      </c>
+      <c r="Y191">
+        <v>-649635.83966857602</v>
+      </c>
+    </row>
+    <row r="192" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A192" s="4">
         <v>1313</v>
       </c>
@@ -14857,8 +17163,20 @@
       <c r="U192" s="11" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="193" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V192">
+        <v>63.5</v>
+      </c>
+      <c r="W192">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X192">
+        <v>-1100898.9178994901</v>
+      </c>
+      <c r="Y192">
+        <v>-640350.85257061105</v>
+      </c>
+    </row>
+    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A193" s="4">
         <v>923</v>
       </c>
@@ -14922,8 +17240,20 @@
       <c r="U193" s="11" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="194" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V193">
+        <v>63.5</v>
+      </c>
+      <c r="W193">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X193">
+        <v>-1104009.3975857</v>
+      </c>
+      <c r="Y193">
+        <v>-637686.64401040401</v>
+      </c>
+    </row>
+    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A194" s="4">
         <v>881</v>
       </c>
@@ -14987,8 +17317,20 @@
       <c r="U194" s="11" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="195" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V194">
+        <v>63.5</v>
+      </c>
+      <c r="W194">
+        <v>4.5</v>
+      </c>
+      <c r="X194">
+        <v>-1109532.6079643201</v>
+      </c>
+      <c r="Y194">
+        <v>-638330.35899632098</v>
+      </c>
+    </row>
+    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A195" s="4">
         <v>877</v>
       </c>
@@ -15052,8 +17394,20 @@
       <c r="U195" s="11" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="196" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V195">
+        <v>63.5</v>
+      </c>
+      <c r="W195">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X195">
+        <v>-1101940.5185656999</v>
+      </c>
+      <c r="Y195">
+        <v>-631392.07064208295</v>
+      </c>
+    </row>
+    <row r="196" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A196" s="4">
         <v>2178</v>
       </c>
@@ -15117,8 +17471,20 @@
       <c r="U196" s="11" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="197" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V196">
+        <v>63.5</v>
+      </c>
+      <c r="W196">
+        <v>5.6</v>
+      </c>
+      <c r="X196">
+        <v>-1110226.4311893899</v>
+      </c>
+      <c r="Y196">
+        <v>-632348.48697839701</v>
+      </c>
+    </row>
+    <row r="197" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A197" s="4">
         <v>1294</v>
       </c>
@@ -15182,8 +17548,20 @@
       <c r="U197" s="11" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="198" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V197">
+        <v>63.5</v>
+      </c>
+      <c r="W197">
+        <v>4.3</v>
+      </c>
+      <c r="X197">
+        <v>-1105729.7869400401</v>
+      </c>
+      <c r="Y197">
+        <v>-622745.78011964995</v>
+      </c>
+    </row>
+    <row r="198" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A198" s="4">
         <v>1540</v>
       </c>
@@ -15247,8 +17625,20 @@
       <c r="U198" s="11" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="199" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V198">
+        <v>93</v>
+      </c>
+      <c r="W198">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X198">
+        <v>-1109690.4132087</v>
+      </c>
+      <c r="Y198">
+        <v>-586868.501224951</v>
+      </c>
+    </row>
+    <row r="199" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A199" s="4">
         <v>707</v>
       </c>
@@ -15312,8 +17702,20 @@
       <c r="U199" s="11" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="200" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V199">
+        <v>93.5</v>
+      </c>
+      <c r="W199">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X199">
+        <v>-1112127.6851192401</v>
+      </c>
+      <c r="Y199">
+        <v>-535728.28204991005</v>
+      </c>
+    </row>
+    <row r="200" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
         <v>614</v>
       </c>
@@ -15377,8 +17779,20 @@
       <c r="U200" s="11" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="201" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V200">
+        <v>67.5</v>
+      </c>
+      <c r="W200">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X200">
+        <v>-1128218.4653916799</v>
+      </c>
+      <c r="Y200">
+        <v>-449563.76397058897</v>
+      </c>
+    </row>
+    <row r="201" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A201" s="4">
         <v>2158</v>
       </c>
@@ -15442,8 +17856,20 @@
       <c r="U201" s="11" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="202" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V201">
+        <v>83</v>
+      </c>
+      <c r="W201">
+        <v>6</v>
+      </c>
+      <c r="X201">
+        <v>-1129184.25122899</v>
+      </c>
+      <c r="Y201">
+        <v>-437557.55524459301</v>
+      </c>
+    </row>
+    <row r="202" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A202" s="4">
         <v>709</v>
       </c>
@@ -15507,8 +17933,20 @@
       <c r="U202" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="203" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V202">
+        <v>89.5</v>
+      </c>
+      <c r="W202">
+        <v>4.3</v>
+      </c>
+      <c r="X202">
+        <v>-1079090.5501989599</v>
+      </c>
+      <c r="Y202">
+        <v>-877341.84773451404</v>
+      </c>
+    </row>
+    <row r="203" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
         <v>736</v>
       </c>
@@ -15572,8 +18010,20 @@
       <c r="U203" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="204" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V203">
+        <v>89.5</v>
+      </c>
+      <c r="W203">
+        <v>3</v>
+      </c>
+      <c r="X203">
+        <v>-1084580.1715049699</v>
+      </c>
+      <c r="Y203">
+        <v>-878230.60093769804</v>
+      </c>
+    </row>
+    <row r="204" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
         <v>655</v>
       </c>
@@ -15637,8 +18087,20 @@
       <c r="U204" s="11" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="205" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V204">
+        <v>91.5</v>
+      </c>
+      <c r="W204">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X204">
+        <v>-1087496.3925677401</v>
+      </c>
+      <c r="Y204">
+        <v>-842060.13964297296</v>
+      </c>
+    </row>
+    <row r="205" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
         <v>1144</v>
       </c>
@@ -15702,8 +18164,20 @@
       <c r="U205" s="11" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="206" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V205">
+        <v>99</v>
+      </c>
+      <c r="W205">
+        <v>6</v>
+      </c>
+      <c r="X205">
+        <v>-1087938.7345630301</v>
+      </c>
+      <c r="Y205">
+        <v>-820788.01939543604</v>
+      </c>
+    </row>
+    <row r="206" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
         <v>158</v>
       </c>
@@ -15767,8 +18241,20 @@
       <c r="U206" s="11" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="207" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V206">
+        <v>79.5</v>
+      </c>
+      <c r="W206">
+        <v>5</v>
+      </c>
+      <c r="X206">
+        <v>-1092917.74251433</v>
+      </c>
+      <c r="Y206">
+        <v>-806298.080518584</v>
+      </c>
+    </row>
+    <row r="207" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
         <v>1145</v>
       </c>
@@ -15832,8 +18318,20 @@
       <c r="U207" s="11" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="208" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V207">
+        <v>75</v>
+      </c>
+      <c r="W207">
+        <v>5.3</v>
+      </c>
+      <c r="X207">
+        <v>-1094780.71395877</v>
+      </c>
+      <c r="Y207">
+        <v>-812671.45562149398</v>
+      </c>
+    </row>
+    <row r="208" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
         <v>92</v>
       </c>
@@ -15897,8 +18395,20 @@
       <c r="U208" s="11" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="209" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V208">
+        <v>79.5</v>
+      </c>
+      <c r="W208">
+        <v>5</v>
+      </c>
+      <c r="X208">
+        <v>-1091484.6563655699</v>
+      </c>
+      <c r="Y208">
+        <v>-796949.17818619404</v>
+      </c>
+    </row>
+    <row r="209" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
         <v>794</v>
       </c>
@@ -15962,8 +18472,20 @@
       <c r="U209" s="11" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="210" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V209">
+        <v>79.5</v>
+      </c>
+      <c r="W209">
+        <v>5.6</v>
+      </c>
+      <c r="X209">
+        <v>-1094235.65918357</v>
+      </c>
+      <c r="Y209">
+        <v>-797352.10857672303</v>
+      </c>
+    </row>
+    <row r="210" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
         <v>1963</v>
       </c>
@@ -16027,8 +18549,20 @@
       <c r="U210" s="11" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="211" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V210">
+        <v>79.5</v>
+      </c>
+      <c r="W210">
+        <v>4.7</v>
+      </c>
+      <c r="X210">
+        <v>-1095105.95879966</v>
+      </c>
+      <c r="Y210">
+        <v>-791386.936565271</v>
+      </c>
+    </row>
+    <row r="211" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
         <v>1731</v>
       </c>
@@ -16092,8 +18626,20 @@
       <c r="U211" s="11" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="212" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V211">
+        <v>67</v>
+      </c>
+      <c r="W211">
+        <v>5.4</v>
+      </c>
+      <c r="X211">
+        <v>-1100286.96670276</v>
+      </c>
+      <c r="Y211">
+        <v>-734300.870268628</v>
+      </c>
+    </row>
+    <row r="212" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A212" s="4">
         <v>1603</v>
       </c>
@@ -16157,8 +18703,20 @@
       <c r="U212" s="11" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V212">
+        <v>83</v>
+      </c>
+      <c r="W212">
+        <v>6.1</v>
+      </c>
+      <c r="X212">
+        <v>-1110937.4556283799</v>
+      </c>
+      <c r="Y212">
+        <v>-717467.87578611798</v>
+      </c>
+    </row>
+    <row r="213" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A213" s="4">
         <v>465</v>
       </c>
@@ -16222,8 +18780,20 @@
       <c r="U213" s="11" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="214" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V213">
+        <v>89.5</v>
+      </c>
+      <c r="W213">
+        <v>5.4</v>
+      </c>
+      <c r="X213">
+        <v>-1109349.9074303899</v>
+      </c>
+      <c r="Y213">
+        <v>-708135.33863165404</v>
+      </c>
+    </row>
+    <row r="214" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A214" s="4">
         <v>2174</v>
       </c>
@@ -16287,8 +18857,20 @@
       <c r="U214" s="11" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="215" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V214">
+        <v>66</v>
+      </c>
+      <c r="W214">
+        <v>4.5</v>
+      </c>
+      <c r="X214">
+        <v>-1115333.04304946</v>
+      </c>
+      <c r="Y214">
+        <v>-660258.37496847799</v>
+      </c>
+    </row>
+    <row r="215" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A215" s="4">
         <v>1784</v>
       </c>
@@ -16352,8 +18934,20 @@
       <c r="U215" s="11" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="216" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V215">
+        <v>63.5</v>
+      </c>
+      <c r="W215">
+        <v>4.2</v>
+      </c>
+      <c r="X215">
+        <v>-1117115.7975196501</v>
+      </c>
+      <c r="Y215">
+        <v>-645286.18016918504</v>
+      </c>
+    </row>
+    <row r="216" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A216" s="4">
         <v>859</v>
       </c>
@@ -16417,8 +19011,20 @@
       <c r="U216" s="11" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="217" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V216">
+        <v>89.5</v>
+      </c>
+      <c r="W216">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X216">
+        <v>-1126916.45357264</v>
+      </c>
+      <c r="Y216">
+        <v>-582643.71267108305</v>
+      </c>
+    </row>
+    <row r="217" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A217" s="4">
         <v>367</v>
       </c>
@@ -16482,8 +19088,20 @@
       <c r="U217" s="11" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="218" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V217">
+        <v>89.5</v>
+      </c>
+      <c r="W217">
+        <v>4.3</v>
+      </c>
+      <c r="X217">
+        <v>-1127233.4719773801</v>
+      </c>
+      <c r="Y217">
+        <v>-579643.25094035396</v>
+      </c>
+    </row>
+    <row r="218" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
         <v>1916</v>
       </c>
@@ -16547,8 +19165,20 @@
       <c r="U218" s="11" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="219" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V218">
+        <v>89.5</v>
+      </c>
+      <c r="W218">
+        <v>4.5</v>
+      </c>
+      <c r="X218">
+        <v>-1127548.8376843501</v>
+      </c>
+      <c r="Y218">
+        <v>-576642.61244409904</v>
+      </c>
+    </row>
+    <row r="219" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
         <v>1499</v>
       </c>
@@ -16612,8 +19242,20 @@
       <c r="U219" s="11" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="220" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V219">
+        <v>89.5</v>
+      </c>
+      <c r="W219">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X219">
+        <v>-1127862.5508141399</v>
+      </c>
+      <c r="Y219">
+        <v>-573641.79851557303</v>
+      </c>
+    </row>
+    <row r="220" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
         <v>560</v>
       </c>
@@ -16677,8 +19319,20 @@
       <c r="U220" s="11" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="221" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V220" t="s">
+        <v>627</v>
+      </c>
+      <c r="W220">
+        <v>4.8</v>
+      </c>
+      <c r="X220">
+        <v>-1136241.9177788801</v>
+      </c>
+      <c r="Y220">
+        <v>-486545.58443767199</v>
+      </c>
+    </row>
+    <row r="221" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
         <v>1367</v>
       </c>
@@ -16742,8 +19396,20 @@
       <c r="U221" s="11" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="222" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V221">
+        <v>68.5</v>
+      </c>
+      <c r="W221">
+        <v>6.3</v>
+      </c>
+      <c r="X221">
+        <v>-1136506.11395068</v>
+      </c>
+      <c r="Y221">
+        <v>-483539.89762271597</v>
+      </c>
+    </row>
+    <row r="222" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
         <v>1439</v>
       </c>
@@ -16807,8 +19473,20 @@
       <c r="U222" s="11" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="223" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V222">
+        <v>84.5</v>
+      </c>
+      <c r="W222">
+        <v>4.7</v>
+      </c>
+      <c r="X222">
+        <v>-1129235.4341488001</v>
+      </c>
+      <c r="Y222">
+        <v>-470805.82775863999</v>
+      </c>
+    </row>
+    <row r="223" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
         <v>1438</v>
       </c>
@@ -16872,8 +19550,20 @@
       <c r="U223" s="11" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="224" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V223">
+        <v>84.5</v>
+      </c>
+      <c r="W223">
+        <v>5.9</v>
+      </c>
+      <c r="X223">
+        <v>-1132005.7870129901</v>
+      </c>
+      <c r="Y223">
+        <v>-471042.43998947402</v>
+      </c>
+    </row>
+    <row r="224" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A224" s="4">
         <v>1554</v>
       </c>
@@ -16937,8 +19627,20 @@
       <c r="U224" s="11" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="225" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V224">
+        <v>80.5</v>
+      </c>
+      <c r="W224">
+        <v>4.2</v>
+      </c>
+      <c r="X224">
+        <v>-1136768.6616980101</v>
+      </c>
+      <c r="Y224">
+        <v>-480534.06207253202</v>
+      </c>
+    </row>
+    <row r="225" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
         <v>605</v>
       </c>
@@ -17002,8 +19704,20 @@
       <c r="U225" s="11" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="226" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V225" t="s">
+        <v>627</v>
+      </c>
+      <c r="W225">
+        <v>5</v>
+      </c>
+      <c r="X225">
+        <v>-1137288.81311717</v>
+      </c>
+      <c r="Y225">
+        <v>-474521.947707891</v>
+      </c>
+    </row>
+    <row r="226" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
         <v>1437</v>
       </c>
@@ -17067,8 +19781,20 @@
       <c r="U226" s="11" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="227" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V226" t="s">
+        <v>627</v>
+      </c>
+      <c r="W226">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X226">
+        <v>-1137546.4163929201</v>
+      </c>
+      <c r="Y226">
+        <v>-471515.67047946597</v>
+      </c>
+    </row>
+    <row r="227" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
         <v>2015</v>
       </c>
@@ -17132,8 +19858,20 @@
       <c r="U227" s="11" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="228" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V227">
+        <v>93.5</v>
+      </c>
+      <c r="W227">
+        <v>4.5</v>
+      </c>
+      <c r="X227">
+        <v>-1132515.51734716</v>
+      </c>
+      <c r="Y227">
+        <v>-465035.52406414202</v>
+      </c>
+    </row>
+    <row r="228" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
         <v>568</v>
       </c>
@@ -17197,8 +19935,20 @@
       <c r="U228" s="11" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="229" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V228">
+        <v>83</v>
+      </c>
+      <c r="W228">
+        <v>5.6</v>
+      </c>
+      <c r="X228">
+        <v>-1129997.1610788</v>
+      </c>
+      <c r="Y228">
+        <v>-461799.79275501601</v>
+      </c>
+    </row>
+    <row r="229" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
         <v>895</v>
       </c>
@@ -17262,8 +20012,20 @@
       <c r="U229" s="11" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="230" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V229">
+        <v>83</v>
+      </c>
+      <c r="W229">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X229">
+        <v>-1130247.77956226</v>
+      </c>
+      <c r="Y229">
+        <v>-458797.493794073</v>
+      </c>
+    </row>
+    <row r="230" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A230" s="4">
         <v>1790</v>
       </c>
@@ -17327,8 +20089,20 @@
       <c r="U230" s="11" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="231" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V230">
+        <v>83</v>
+      </c>
+      <c r="W230">
+        <v>4.5</v>
+      </c>
+      <c r="X230">
+        <v>-1132767.91349086</v>
+      </c>
+      <c r="Y230">
+        <v>-462031.84992845898</v>
+      </c>
+    </row>
+    <row r="231" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A231" s="4">
         <v>1390</v>
       </c>
@@ -17392,8 +20166,20 @@
       <c r="U231" s="11" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="232" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V231">
+        <v>83</v>
+      </c>
+      <c r="W231">
+        <v>6.2</v>
+      </c>
+      <c r="X231">
+        <v>-1133018.6637659301</v>
+      </c>
+      <c r="Y231">
+        <v>-459028.03270007198</v>
+      </c>
+    </row>
+    <row r="232" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A232" s="4">
         <v>1708</v>
       </c>
@@ -17457,8 +20243,20 @@
       <c r="U232" s="11" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="233" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V232">
+        <v>84.5</v>
+      </c>
+      <c r="W232">
+        <v>5.3</v>
+      </c>
+      <c r="X232">
+        <v>-1137802.3718760801</v>
+      </c>
+      <c r="Y232">
+        <v>-468509.24801869702</v>
+      </c>
+    </row>
+    <row r="233" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
         <v>858</v>
       </c>
@@ -17522,8 +20320,20 @@
       <c r="U233" s="11" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="234" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V233">
+        <v>93.5</v>
+      </c>
+      <c r="W233">
+        <v>6</v>
+      </c>
+      <c r="X233">
+        <v>-1138056.67969906</v>
+      </c>
+      <c r="Y233">
+        <v>-465502.68123273499</v>
+      </c>
+    </row>
+    <row r="234" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
         <v>566</v>
       </c>
@@ -17587,8 +20397,20 @@
       <c r="U234" s="11" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="235" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V234">
+        <v>79.5</v>
+      </c>
+      <c r="W234">
+        <v>10</v>
+      </c>
+      <c r="X234">
+        <v>-1135538.63969469</v>
+      </c>
+      <c r="Y234">
+        <v>-462263.90933444398</v>
+      </c>
+    </row>
+    <row r="235" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A235" s="4">
         <v>2106</v>
       </c>
@@ -17652,8 +20474,20 @@
       <c r="U235" s="11" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="236" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V235">
+        <v>83</v>
+      </c>
+      <c r="W235">
+        <v>6.5</v>
+      </c>
+      <c r="X235">
+        <v>-1135789.52151769</v>
+      </c>
+      <c r="Y235">
+        <v>-459258.57404829498</v>
+      </c>
+    </row>
+    <row r="236" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A236" s="4">
         <v>564</v>
       </c>
@@ -17717,8 +20551,20 @@
       <c r="U236" s="11" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="237" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V236">
+        <v>79.5</v>
+      </c>
+      <c r="W236">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="X236">
+        <v>-1138309.3401347201</v>
+      </c>
+      <c r="Y236">
+        <v>-462495.97082954802</v>
+      </c>
+    </row>
+    <row r="237" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A237" s="4">
         <v>1389</v>
       </c>
@@ -17782,8 +20628,20 @@
       <c r="U237" s="11" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="238" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V237">
+        <v>83</v>
+      </c>
+      <c r="W237">
+        <v>6.2</v>
+      </c>
+      <c r="X237">
+        <v>-1138560.3531182001</v>
+      </c>
+      <c r="Y237">
+        <v>-459489.11736889399</v>
+      </c>
+    </row>
+    <row r="238" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
         <v>1469</v>
       </c>
@@ -17847,8 +20705,20 @@
       <c r="U238" s="11" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="239" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V238">
+        <v>83</v>
+      </c>
+      <c r="W238">
+        <v>7.4</v>
+      </c>
+      <c r="X238">
+        <v>-1130496.75330957</v>
+      </c>
+      <c r="Y238">
+        <v>-455795.05274413101</v>
+      </c>
+    </row>
+    <row r="239" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
         <v>889</v>
       </c>
@@ -17912,8 +20782,20 @@
       <c r="U239" s="11" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="240" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V239">
+        <v>83</v>
+      </c>
+      <c r="W239">
+        <v>7.9</v>
+      </c>
+      <c r="X239">
+        <v>-1133267.76824945</v>
+      </c>
+      <c r="Y239">
+        <v>-456024.07373933197</v>
+      </c>
+    </row>
+    <row r="240" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
         <v>915</v>
       </c>
@@ -17977,8 +20859,20 @@
       <c r="U240" s="11" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="241" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V240">
+        <v>83</v>
+      </c>
+      <c r="W240">
+        <v>6.4</v>
+      </c>
+      <c r="X240">
+        <v>-1133515.2274968</v>
+      </c>
+      <c r="Y240">
+        <v>-453019.973189404</v>
+      </c>
+    </row>
+    <row r="241" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
         <v>1993</v>
       </c>
@@ -18042,8 +20936,20 @@
       <c r="U241" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="242" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V241">
+        <v>87</v>
+      </c>
+      <c r="W241">
+        <v>5.8</v>
+      </c>
+      <c r="X241">
+        <v>-1131233.8068152401</v>
+      </c>
+      <c r="Y241">
+        <v>-446786.884505091</v>
+      </c>
+    </row>
+    <row r="242" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
         <v>610</v>
       </c>
@@ -18107,8 +21013,20 @@
       <c r="U242" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="243" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V242">
+        <v>87</v>
+      </c>
+      <c r="W242">
+        <v>7.2</v>
+      </c>
+      <c r="X242">
+        <v>-1133761.0409319999</v>
+      </c>
+      <c r="Y242">
+        <v>-450015.73228671798</v>
+      </c>
+    </row>
+    <row r="243" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
         <v>1992</v>
       </c>
@@ -18172,8 +21090,20 @@
       <c r="U243" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="244" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V243">
+        <v>87</v>
+      </c>
+      <c r="W243">
+        <v>7.5</v>
+      </c>
+      <c r="X243">
+        <v>-1134005.2091793299</v>
+      </c>
+      <c r="Y243">
+        <v>-447011.35223700199</v>
+      </c>
+    </row>
+    <row r="244" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
         <v>1468</v>
       </c>
@@ -18237,8 +21167,20 @@
       <c r="U244" s="11" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="245" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V244">
+        <v>83</v>
+      </c>
+      <c r="W244">
+        <v>6.3</v>
+      </c>
+      <c r="X244">
+        <v>-1136038.7566893599</v>
+      </c>
+      <c r="Y244">
+        <v>-456253.09673453902</v>
+      </c>
+    </row>
+    <row r="245" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
         <v>1467</v>
       </c>
@@ -18302,8 +21244,20 @@
       <c r="U245" s="11" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="246" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V245">
+        <v>83</v>
+      </c>
+      <c r="W245">
+        <v>5.8</v>
+      </c>
+      <c r="X245">
+        <v>-1138809.71855372</v>
+      </c>
+      <c r="Y245">
+        <v>-456482.12196604803</v>
+      </c>
+    </row>
+    <row r="246" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
         <v>1643</v>
       </c>
@@ -18367,8 +21321,20 @@
       <c r="U246" s="11" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="247" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V246">
+        <v>88</v>
+      </c>
+      <c r="W246">
+        <v>5.6</v>
+      </c>
+      <c r="X246">
+        <v>-1139057.4371404101</v>
+      </c>
+      <c r="Y246">
+        <v>-453474.98609064601</v>
+      </c>
+    </row>
+    <row r="247" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
         <v>1991</v>
       </c>
@@ -18432,8 +21398,20 @@
       <c r="U247" s="11" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="248" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V247">
+        <v>93.5</v>
+      </c>
+      <c r="W247">
+        <v>4</v>
+      </c>
+      <c r="X247">
+        <v>-1136776.58443156</v>
+      </c>
+      <c r="Y247">
+        <v>-447235.82258501998</v>
+      </c>
+    </row>
+    <row r="248" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
         <v>606</v>
       </c>
@@ -18497,8 +21475,20 @@
       <c r="U248" s="11" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="249" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V248">
+        <v>88</v>
+      </c>
+      <c r="W248">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X248">
+        <v>-1139303.5083606101</v>
+      </c>
+      <c r="Y248">
+        <v>-450467.71021945198</v>
+      </c>
+    </row>
+    <row r="249" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
         <v>1990</v>
       </c>
@@ -18562,8 +21552,20 @@
       <c r="U249" s="11" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="250" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V249">
+        <v>87</v>
+      </c>
+      <c r="W249">
+        <v>5.8</v>
+      </c>
+      <c r="X249">
+        <v>-1139547.93263501</v>
+      </c>
+      <c r="Y249">
+        <v>-447460.29449100897</v>
+      </c>
+    </row>
+    <row r="250" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
         <v>1617</v>
       </c>
@@ -18627,8 +21629,20 @@
       <c r="U250" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="251" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V250">
+        <v>87</v>
+      </c>
+      <c r="W250">
+        <v>5</v>
+      </c>
+      <c r="X250">
+        <v>-1134247.73250246</v>
+      </c>
+      <c r="Y250">
+        <v>-444006.83345060598</v>
+      </c>
+    </row>
+    <row r="251" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A251" s="4">
         <v>1616</v>
       </c>
@@ -18692,8 +21706,20 @@
       <c r="U251" s="11" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="252" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V251">
+        <v>88</v>
+      </c>
+      <c r="W251">
+        <v>4.2</v>
+      </c>
+      <c r="X251">
+        <v>-1137019.2348666</v>
+      </c>
+      <c r="Y251">
+        <v>-444229.78618256102</v>
+      </c>
+    </row>
+    <row r="252" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A252" s="4">
         <v>1885</v>
       </c>
@@ -18757,8 +21783,20 @@
       <c r="U252" s="11" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="253" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V252">
+        <v>88</v>
+      </c>
+      <c r="W252">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X252">
+        <v>-1137260.2396897599</v>
+      </c>
+      <c r="Y252">
+        <v>-441223.61239618401</v>
+      </c>
+    </row>
+    <row r="253" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
         <v>911</v>
       </c>
@@ -18822,8 +21860,20 @@
       <c r="U253" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="254" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V253">
+        <v>87</v>
+      </c>
+      <c r="W253">
+        <v>6.1</v>
+      </c>
+      <c r="X253">
+        <v>-1139790.7103066901</v>
+      </c>
+      <c r="Y253">
+        <v>-444452.74067790899</v>
+      </c>
+    </row>
+    <row r="254" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
         <v>1884</v>
       </c>
@@ -18887,8 +21937,20 @@
       <c r="U254" s="11" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="255" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V254">
+        <v>88</v>
+      </c>
+      <c r="W254">
+        <v>4.3</v>
+      </c>
+      <c r="X254">
+        <v>-1140031.8412907801</v>
+      </c>
+      <c r="Y254">
+        <v>-441445.04971765901</v>
+      </c>
+    </row>
+    <row r="255" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
         <v>1962</v>
       </c>
@@ -18952,8 +22014,20 @@
       <c r="U255" s="11" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="256" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V255">
+        <v>88</v>
+      </c>
+      <c r="W255">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X255">
+        <v>-1137499.5983613899</v>
+      </c>
+      <c r="Y255">
+        <v>-438217.30208323</v>
+      </c>
+    </row>
+    <row r="256" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
         <v>2067</v>
       </c>
@@ -19017,8 +22091,20 @@
       <c r="U256" s="11" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="257" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V256">
+        <v>88</v>
+      </c>
+      <c r="W256">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X256">
+        <v>-1137737.3113719299</v>
+      </c>
+      <c r="Y256">
+        <v>-435210.85594431299</v>
+      </c>
+    </row>
+    <row r="257" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
         <v>2157</v>
       </c>
@@ -19082,8 +22168,20 @@
       <c r="U257" s="11" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="258" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V257">
+        <v>88</v>
+      </c>
+      <c r="W257">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X257">
+        <v>-1140271.3255646499</v>
+      </c>
+      <c r="Y257">
+        <v>-438437.22198932001</v>
+      </c>
+    </row>
+    <row r="258" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
         <v>706</v>
       </c>
@@ -19147,8 +22245,20 @@
       <c r="U258" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="259" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V258">
+        <v>89.5</v>
+      </c>
+      <c r="W258">
+        <v>3.4</v>
+      </c>
+      <c r="X258">
+        <v>-1091031.40287944</v>
+      </c>
+      <c r="Y258">
+        <v>-873158.31030315696</v>
+      </c>
+    </row>
+    <row r="259" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
         <v>692</v>
       </c>
@@ -19212,8 +22322,20 @@
       <c r="U259" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="260" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V259">
+        <v>89.5</v>
+      </c>
+      <c r="W259">
+        <v>4.5</v>
+      </c>
+      <c r="X259">
+        <v>-1099746.3340978101</v>
+      </c>
+      <c r="Y259">
+        <v>-871496.60802625795</v>
+      </c>
+    </row>
+    <row r="260" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
         <v>1482</v>
       </c>
@@ -19277,8 +22399,20 @@
       <c r="U260" s="11" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="261" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V260">
+        <v>66</v>
+      </c>
+      <c r="W260">
+        <v>5.4</v>
+      </c>
+      <c r="X260">
+        <v>-1119762.93668728</v>
+      </c>
+      <c r="Y260">
+        <v>-669913.54161365202</v>
+      </c>
+    </row>
+    <row r="261" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A261" s="4">
         <v>726</v>
       </c>
@@ -19342,8 +22476,20 @@
       <c r="U261" s="11" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="262" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V261">
+        <v>66</v>
+      </c>
+      <c r="W261">
+        <v>5</v>
+      </c>
+      <c r="X261">
+        <v>-1122155.5820355299</v>
+      </c>
+      <c r="Y261">
+        <v>-673248.479477357</v>
+      </c>
+    </row>
+    <row r="262" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
         <v>936</v>
       </c>
@@ -19407,8 +22553,20 @@
       <c r="U262" s="11" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="263" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V262">
+        <v>66</v>
+      </c>
+      <c r="W262">
+        <v>5.2</v>
+      </c>
+      <c r="X262">
+        <v>-1122522.6294312601</v>
+      </c>
+      <c r="Y262">
+        <v>-670250.65846446704</v>
+      </c>
+    </row>
+    <row r="263" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
         <v>2176</v>
       </c>
@@ -19472,8 +22630,20 @@
       <c r="U263" s="11" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="264" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V263">
+        <v>75.5</v>
+      </c>
+      <c r="W263">
+        <v>5.2</v>
+      </c>
+      <c r="X263">
+        <v>-1126797.8457529</v>
+      </c>
+      <c r="Y263">
+        <v>-634261.30716780003</v>
+      </c>
+    </row>
+    <row r="264" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
         <v>1747</v>
       </c>
@@ -19537,8 +22707,20 @@
       <c r="U264" s="11" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="265" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V264">
+        <v>75.5</v>
+      </c>
+      <c r="W264">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X264">
+        <v>-1132321.5423640001</v>
+      </c>
+      <c r="Y264">
+        <v>-634898.90624239703</v>
+      </c>
+    </row>
+    <row r="265" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
         <v>1662</v>
       </c>
@@ -19602,8 +22784,20 @@
       <c r="U265" s="11" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="266" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V265">
+        <v>75.5</v>
+      </c>
+      <c r="W265">
+        <v>5</v>
+      </c>
+      <c r="X265">
+        <v>-1129905.3696711401</v>
+      </c>
+      <c r="Y265">
+        <v>-631578.20319680905</v>
+      </c>
+    </row>
+    <row r="266" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
         <v>1558</v>
       </c>
@@ -19667,8 +22861,20 @@
       <c r="U266" s="11" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="267" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V266">
+        <v>85.5</v>
+      </c>
+      <c r="W266">
+        <v>2.4</v>
+      </c>
+      <c r="X266">
+        <v>-1131806.32969059</v>
+      </c>
+      <c r="Y266">
+        <v>-589235.97185077297</v>
+      </c>
+    </row>
+    <row r="267" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
         <v>856</v>
       </c>
@@ -19732,8 +22938,20 @@
       <c r="U267" s="11" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="268" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V267">
+        <v>89.5</v>
+      </c>
+      <c r="W267">
+        <v>4.7</v>
+      </c>
+      <c r="X267">
+        <v>-1129681.2265951999</v>
+      </c>
+      <c r="Y267">
+        <v>-582936.600718359</v>
+      </c>
+    </row>
+    <row r="268" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
         <v>365</v>
       </c>
@@ -19797,8 +23015,20 @@
       <c r="U268" s="11" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="269" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V268">
+        <v>89.5</v>
+      </c>
+      <c r="W268">
+        <v>4.2</v>
+      </c>
+      <c r="X268">
+        <v>-1132763.3278572999</v>
+      </c>
+      <c r="Y268">
+        <v>-580225.98092794104</v>
+      </c>
+    </row>
+    <row r="269" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
         <v>1557</v>
       </c>
@@ -19862,8 +23092,20 @@
       <c r="U269" s="11" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="270" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V269">
+        <v>85.5</v>
+      </c>
+      <c r="W269">
+        <v>5</v>
+      </c>
+      <c r="X269">
+        <v>-1134570.7420558401</v>
+      </c>
+      <c r="Y269">
+        <v>-589531.90607674699</v>
+      </c>
+    </row>
+    <row r="270" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A270" s="4">
         <v>665</v>
       </c>
@@ -19927,8 +23169,20 @@
       <c r="U270" s="11" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="271" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V270">
+        <v>89.5</v>
+      </c>
+      <c r="W270">
+        <v>4.5</v>
+      </c>
+      <c r="X270">
+        <v>-1138293.1169302</v>
+      </c>
+      <c r="Y270">
+        <v>-580808.71005925303</v>
+      </c>
+    </row>
+    <row r="271" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A271" s="4">
         <v>1915</v>
       </c>
@@ -19992,8 +23246,20 @@
       <c r="U271" s="11" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="272" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V271">
+        <v>89.5</v>
+      </c>
+      <c r="W271">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X271">
+        <v>-1133079.01837187</v>
+      </c>
+      <c r="Y271">
+        <v>-577222.29628756701</v>
+      </c>
+    </row>
+    <row r="272" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A272" s="4">
         <v>635</v>
       </c>
@@ -20057,8 +23323,20 @@
       <c r="U272" s="11" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="273" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V272">
+        <v>69</v>
+      </c>
+      <c r="W272">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X272">
+        <v>-1143475.6977698701</v>
+      </c>
+      <c r="Y272">
+        <v>-499317.69594767602</v>
+      </c>
+    </row>
+    <row r="273" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
         <v>892</v>
       </c>
@@ -20122,8 +23400,20 @@
       <c r="U273" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="274" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V273">
+        <v>87</v>
+      </c>
+      <c r="W273">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X273">
+        <v>-1139275.84939073</v>
+      </c>
+      <c r="Y273">
+        <v>-483782.590117632</v>
+      </c>
+    </row>
+    <row r="274" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
         <v>1636</v>
       </c>
@@ -20187,8 +23477,20 @@
       <c r="U274" s="11" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="275" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V274">
+        <v>83.5</v>
+      </c>
+      <c r="W274" t="s">
+        <v>627</v>
+      </c>
+      <c r="X274">
+        <v>-1147320.1716994999</v>
+      </c>
+      <c r="Y274">
+        <v>-487522.44024172</v>
+      </c>
+    </row>
+    <row r="275" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
         <v>1366</v>
       </c>
@@ -20252,8 +23554,20 @@
       <c r="U275" s="11" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="276" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V275">
+        <v>83.5</v>
+      </c>
+      <c r="W275">
+        <v>8.1</v>
+      </c>
+      <c r="X275">
+        <v>-1147584.9167114</v>
+      </c>
+      <c r="Y275">
+        <v>-484510.67760232801</v>
+      </c>
+    </row>
+    <row r="276" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
         <v>1553</v>
       </c>
@@ -20317,8 +23631,20 @@
       <c r="U276" s="11" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="277" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V276">
+        <v>68.5</v>
+      </c>
+      <c r="W276">
+        <v>5.6</v>
+      </c>
+      <c r="X276">
+        <v>-1139538.5336380601</v>
+      </c>
+      <c r="Y276">
+        <v>-480775.23556748201</v>
+      </c>
+    </row>
+    <row r="277" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
         <v>2034</v>
       </c>
@@ -20382,8 +23708,20 @@
       <c r="U277" s="11" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="278" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V277">
+        <v>77</v>
+      </c>
+      <c r="W277">
+        <v>5.3</v>
+      </c>
+      <c r="X277">
+        <v>-1142569.55332557</v>
+      </c>
+      <c r="Y277">
+        <v>-478007.390012344</v>
+      </c>
+    </row>
+    <row r="278" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
         <v>603</v>
       </c>
@@ -20441,8 +23779,20 @@
       <c r="U278" s="11" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="279" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V278">
+        <v>85</v>
+      </c>
+      <c r="W278">
+        <v>5.3</v>
+      </c>
+      <c r="X278">
+        <v>-1140058.95616134</v>
+      </c>
+      <c r="Y278">
+        <v>-474760.08378873998</v>
+      </c>
+    </row>
+    <row r="279" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
         <v>1436</v>
       </c>
@@ -20506,8 +23856,20 @@
       <c r="U279" s="11" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="280" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V279">
+        <v>93.5</v>
+      </c>
+      <c r="W279">
+        <v>6.2</v>
+      </c>
+      <c r="X279">
+        <v>-1140316.6938046899</v>
+      </c>
+      <c r="Y279">
+        <v>-471752.28865301202</v>
+      </c>
+    </row>
+    <row r="280" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
         <v>601</v>
       </c>
@@ -20571,8 +23933,20 @@
       <c r="U280" s="11" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="281" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V280">
+        <v>80.5</v>
+      </c>
+      <c r="W280">
+        <v>4.2</v>
+      </c>
+      <c r="X280">
+        <v>-1142829.07499745</v>
+      </c>
+      <c r="Y280">
+        <v>-474998.22219802497</v>
+      </c>
+    </row>
+    <row r="281" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A281" s="4">
         <v>1435</v>
       </c>
@@ -20636,8 +24010,20 @@
       <c r="U281" s="11" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="282" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V281">
+        <v>93.5</v>
+      </c>
+      <c r="W281">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X281">
+        <v>-1143086.94708453</v>
+      </c>
+      <c r="Y281">
+        <v>-471988.90832293598</v>
+      </c>
+    </row>
+    <row r="282" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A282" s="4">
         <v>2033</v>
       </c>
@@ -20701,8 +24087,20 @@
       <c r="U282" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="283" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V282">
+        <v>87</v>
+      </c>
+      <c r="W282">
+        <v>5.9</v>
+      </c>
+      <c r="X282">
+        <v>-1148109.45236636</v>
+      </c>
+      <c r="Y282">
+        <v>-478486.70832726703</v>
+      </c>
+    </row>
+    <row r="283" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A283" s="4">
         <v>597</v>
       </c>
@@ -20766,8 +24164,20 @@
       <c r="U283" s="11" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="284" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V283">
+        <v>93.5</v>
+      </c>
+      <c r="W283">
+        <v>5.5</v>
+      </c>
+      <c r="X283">
+        <v>-1148369.2431423599</v>
+      </c>
+      <c r="Y283">
+        <v>-475474.503098674</v>
+      </c>
+    </row>
+    <row r="284" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A284" s="4">
         <v>1433</v>
       </c>
@@ -20831,8 +24241,20 @@
       <c r="U284" s="11" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="285" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V284">
+        <v>93.5</v>
+      </c>
+      <c r="W284">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X284">
+        <v>-1148627.38293671</v>
+      </c>
+      <c r="Y284">
+        <v>-472462.15249179403</v>
+      </c>
+    </row>
+    <row r="285" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A285" s="4">
         <v>1704</v>
       </c>
@@ -20896,8 +24318,20 @@
       <c r="U285" s="11" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="286" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V285">
+        <v>93.5</v>
+      </c>
+      <c r="W285">
+        <v>5</v>
+      </c>
+      <c r="X285">
+        <v>-1140572.7828917101</v>
+      </c>
+      <c r="Y285">
+        <v>-468744.34777784901</v>
+      </c>
+    </row>
+    <row r="286" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A286" s="4">
         <v>2013</v>
       </c>
@@ -20961,8 +24395,20 @@
       <c r="U286" s="11" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="287" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V286">
+        <v>79.5</v>
+      </c>
+      <c r="W286">
+        <v>7.3</v>
+      </c>
+      <c r="X286">
+        <v>-1140827.2233275501</v>
+      </c>
+      <c r="Y286">
+        <v>-465736.26237455301</v>
+      </c>
+    </row>
+    <row r="287" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A287" s="4">
         <v>562</v>
       </c>
@@ -21026,8 +24472,20 @@
       <c r="U287" s="11" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="288" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V287">
+        <v>79.5</v>
+      </c>
+      <c r="W287">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="X287">
+        <v>-1141080.0155470101</v>
+      </c>
+      <c r="Y287">
+        <v>-462728.03400328499</v>
+      </c>
+    </row>
+    <row r="288" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
         <v>1789</v>
       </c>
@@ -21091,8 +24549,20 @@
       <c r="U288" s="11" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="289" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V288">
+        <v>79.5</v>
+      </c>
+      <c r="W288">
+        <v>7.9</v>
+      </c>
+      <c r="X288">
+        <v>-1143850.6660150001</v>
+      </c>
+      <c r="Y288">
+        <v>-462960.09881976299</v>
+      </c>
+    </row>
+    <row r="289" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A289" s="4">
         <v>1387</v>
       </c>
@@ -21156,8 +24626,20 @@
       <c r="U289" s="11" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="290" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V289">
+        <v>79.5</v>
+      </c>
+      <c r="W289">
+        <v>8</v>
+      </c>
+      <c r="X289">
+        <v>-1144101.9408378799</v>
+      </c>
+      <c r="Y289">
+        <v>-459950.209533763</v>
+      </c>
+    </row>
+    <row r="290" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A290" s="4">
         <v>1707</v>
       </c>
@@ -21221,8 +24703,20 @@
       <c r="U290" s="11" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="291" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V290">
+        <v>93.5</v>
+      </c>
+      <c r="W290">
+        <v>5.3</v>
+      </c>
+      <c r="X290">
+        <v>-1146113.53193253</v>
+      </c>
+      <c r="Y290">
+        <v>-469214.55209327902</v>
+      </c>
+    </row>
+    <row r="291" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A291" s="4">
         <v>2012</v>
       </c>
@@ -21286,8 +24780,20 @@
       <c r="U291" s="11" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="292" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V291">
+        <v>83.5</v>
+      </c>
+      <c r="W291">
+        <v>8.9</v>
+      </c>
+      <c r="X291">
+        <v>-1146368.23701947</v>
+      </c>
+      <c r="Y291">
+        <v>-466203.43021806201</v>
+      </c>
+    </row>
+    <row r="292" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A292" s="4">
         <v>1757</v>
       </c>
@@ -21351,8 +24857,20 @@
       <c r="U292" s="11" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="293" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V292">
+        <v>85.5</v>
+      </c>
+      <c r="W292">
+        <v>4.3</v>
+      </c>
+      <c r="X292">
+        <v>-1148883.8711369699</v>
+      </c>
+      <c r="Y292">
+        <v>-469449.65649893897</v>
+      </c>
+    </row>
+    <row r="293" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
         <v>2011</v>
       </c>
@@ -21416,8 +24934,20 @@
       <c r="U293" s="11" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="294" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V293">
+        <v>85.5</v>
+      </c>
+      <c r="W293">
+        <v>4.2</v>
+      </c>
+      <c r="X293">
+        <v>-1149138.7083843199</v>
+      </c>
+      <c r="Y293">
+        <v>-466437.016449171</v>
+      </c>
+    </row>
+    <row r="294" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
         <v>2120</v>
       </c>
@@ -21481,8 +25011,20 @@
       <c r="U294" s="11" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="295" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V294">
+        <v>83.5</v>
+      </c>
+      <c r="W294">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="X294">
+        <v>-1146621.2921913699</v>
+      </c>
+      <c r="Y294">
+        <v>-463192.16540427</v>
+      </c>
+    </row>
+    <row r="295" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A295" s="4">
         <v>2119</v>
       </c>
@@ -21546,8 +25088,20 @@
       <c r="U295" s="11" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="296" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V295">
+        <v>85.5</v>
+      </c>
+      <c r="W295">
+        <v>6</v>
+      </c>
+      <c r="X295">
+        <v>-1149391.89513174</v>
+      </c>
+      <c r="Y295">
+        <v>-463424.23339943797</v>
+      </c>
+    </row>
+    <row r="296" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
         <v>1351</v>
       </c>
@@ -21611,8 +25165,20 @@
       <c r="U296" s="11" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="297" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V296">
+        <v>79.5</v>
+      </c>
+      <c r="W296">
+        <v>10.5</v>
+      </c>
+      <c r="X296">
+        <v>-1141580.6551451001</v>
+      </c>
+      <c r="Y296">
+        <v>-456711.14948872197</v>
+      </c>
+    </row>
+    <row r="297" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
         <v>1464</v>
       </c>
@@ -21676,8 +25242,20 @@
       <c r="U297" s="11" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="298" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V297">
+        <v>80</v>
+      </c>
+      <c r="W297">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X297">
+        <v>-1144351.5666703701</v>
+      </c>
+      <c r="Y297">
+        <v>-456940.17854581302</v>
+      </c>
+    </row>
+    <row r="298" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
         <v>827</v>
       </c>
@@ -21741,8 +25319,20 @@
       <c r="U298" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="299" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V298">
+        <v>89.5</v>
+      </c>
+      <c r="W298">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X298">
+        <v>-1106191.38824938</v>
+      </c>
+      <c r="Y298">
+        <v>-866398.11380652897</v>
+      </c>
+    </row>
+    <row r="299" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
         <v>548</v>
       </c>
@@ -21806,8 +25396,20 @@
       <c r="U299" s="11" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="300" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V299">
+        <v>75</v>
+      </c>
+      <c r="W299">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X299">
+        <v>-1109480.0247829701</v>
+      </c>
+      <c r="Y299">
+        <v>-827100.49254981603</v>
+      </c>
+    </row>
+    <row r="300" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A300" s="4">
         <v>754</v>
       </c>
@@ -21871,8 +25473,20 @@
       <c r="U300" s="11" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="301" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V300">
+        <v>75</v>
+      </c>
+      <c r="W300">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X300">
+        <v>-1109932.54480535</v>
+      </c>
+      <c r="Y300">
+        <v>-824109.45490703499</v>
+      </c>
+    </row>
+    <row r="301" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A301" s="4">
         <v>780</v>
       </c>
@@ -21936,8 +25550,20 @@
       <c r="U301" s="11" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="302" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V301">
+        <v>75</v>
+      </c>
+      <c r="W301">
+        <v>5.4</v>
+      </c>
+      <c r="X301">
+        <v>-1118631.77675122</v>
+      </c>
+      <c r="Y301">
+        <v>-822359.00072271703</v>
+      </c>
+    </row>
+    <row r="302" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
         <v>349</v>
       </c>
@@ -22001,8 +25627,20 @@
       <c r="U302" s="11" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="303" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V302">
+        <v>89.5</v>
+      </c>
+      <c r="W302">
+        <v>5.4</v>
+      </c>
+      <c r="X302">
+        <v>-1128650.3449669699</v>
+      </c>
+      <c r="Y302">
+        <v>-710634.18025233399</v>
+      </c>
+    </row>
+    <row r="303" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A303" s="4">
         <v>929</v>
       </c>
@@ -22066,8 +25704,20 @@
       <c r="U303" s="11" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="304" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V303">
+        <v>66</v>
+      </c>
+      <c r="W303">
+        <v>5.4</v>
+      </c>
+      <c r="X303">
+        <v>-1138712.4257507101</v>
+      </c>
+      <c r="Y303">
+        <v>-675280.29470313306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
         <v>346</v>
       </c>
@@ -22131,8 +25781,20 @@
       <c r="U304" s="11" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="305" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V304">
+        <v>75.5</v>
+      </c>
+      <c r="W304">
+        <v>5.2</v>
+      </c>
+      <c r="X304">
+        <v>-1138535.9226645201</v>
+      </c>
+      <c r="Y304">
+        <v>-629523.35035504401</v>
+      </c>
+    </row>
+    <row r="305" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
         <v>492</v>
       </c>
@@ -22196,8 +25858,20 @@
       <c r="U305" s="11" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="306" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V305">
+        <v>85.5</v>
+      </c>
+      <c r="W305">
+        <v>3.3</v>
+      </c>
+      <c r="X305">
+        <v>-1139452.2556741401</v>
+      </c>
+      <c r="Y305">
+        <v>-596138.68225608603</v>
+      </c>
+    </row>
+    <row r="306" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A306" s="4">
         <v>1961</v>
       </c>
@@ -22261,8 +25935,20 @@
       <c r="U306" s="11" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="307" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V306">
+        <v>66</v>
+      </c>
+      <c r="W306">
+        <v>6.5</v>
+      </c>
+      <c r="X306">
+        <v>-1149823.14489248</v>
+      </c>
+      <c r="Y306">
+        <v>-490779.78928667901</v>
+      </c>
+    </row>
+    <row r="307" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A307" s="4">
         <v>1788</v>
       </c>
@@ -22326,8 +26012,20 @@
       <c r="U307" s="11" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="308" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V307">
+        <v>66</v>
+      </c>
+      <c r="W307">
+        <v>7.8</v>
+      </c>
+      <c r="X307">
+        <v>-1150089.67940453</v>
+      </c>
+      <c r="Y307">
+        <v>-487766.65714723099</v>
+      </c>
+    </row>
+    <row r="308" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A308" s="4">
         <v>1635</v>
       </c>
@@ -22391,8 +26089,20 @@
       <c r="U308" s="11" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="309" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V308">
+        <v>66</v>
+      </c>
+      <c r="W308">
+        <v>7.1</v>
+      </c>
+      <c r="X308">
+        <v>-1152859.16615563</v>
+      </c>
+      <c r="Y308">
+        <v>-488010.87549615197</v>
+      </c>
+    </row>
+    <row r="309" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
         <v>898</v>
       </c>
@@ -22456,8 +26166,20 @@
       <c r="U309" s="11" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="310" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V309">
+        <v>85.5</v>
+      </c>
+      <c r="W309">
+        <v>5.5</v>
+      </c>
+      <c r="X309">
+        <v>-1151397.5665659001</v>
+      </c>
+      <c r="Y309">
+        <v>-472698.77613318898</v>
+      </c>
+    </row>
+    <row r="310" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
         <v>1432</v>
       </c>
@@ -22515,8 +26237,20 @@
       <c r="U310" s="11" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="311" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V310">
+        <v>85</v>
+      </c>
+      <c r="W310">
+        <v>5.2</v>
+      </c>
+      <c r="X310">
+        <v>-1154167.72800643</v>
+      </c>
+      <c r="Y310">
+        <v>-472935.40112826799</v>
+      </c>
+    </row>
+    <row r="311" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
         <v>1755</v>
       </c>
@@ -22580,8 +26314,20 @@
       <c r="U311" s="11" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="312" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V311">
+        <v>85.5</v>
+      </c>
+      <c r="W311">
+        <v>4.8</v>
+      </c>
+      <c r="X311">
+        <v>-1151654.1875774299</v>
+      </c>
+      <c r="Y311">
+        <v>-469684.76199400303</v>
+      </c>
+    </row>
+    <row r="312" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
         <v>2010</v>
       </c>
@@ -22645,8 +26391,20 @@
       <c r="U312" s="11" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="313" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V312">
+        <v>85.5</v>
+      </c>
+      <c r="W312">
+        <v>5.4</v>
+      </c>
+      <c r="X312">
+        <v>-1151909.1570607701</v>
+      </c>
+      <c r="Y312">
+        <v>-466670.60403373302</v>
+      </c>
+    </row>
+    <row r="313" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
         <v>833</v>
       </c>
@@ -22710,8 +26468,20 @@
       <c r="U313" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="314" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V313">
+        <v>87</v>
+      </c>
+      <c r="W313">
+        <v>3.8</v>
+      </c>
+      <c r="X313">
+        <v>-1126427.66172873</v>
+      </c>
+      <c r="Y313">
+        <v>-845022.31224815804</v>
+      </c>
+    </row>
+    <row r="314" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A314" s="4">
         <v>760</v>
       </c>
@@ -22775,8 +26545,20 @@
       <c r="U314" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="315" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V314">
+        <v>87</v>
+      </c>
+      <c r="W314">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X314">
+        <v>-1124602.5281314</v>
+      </c>
+      <c r="Y314">
+        <v>-838599.73283449502</v>
+      </c>
+    </row>
+    <row r="315" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A315" s="4">
         <v>1162</v>
       </c>
@@ -22840,8 +26622,20 @@
       <c r="U315" s="11" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="316" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V315">
+        <v>75</v>
+      </c>
+      <c r="W315">
+        <v>4.3</v>
+      </c>
+      <c r="X315">
+        <v>-1120929.5019437899</v>
+      </c>
+      <c r="Y315">
+        <v>-825770.00976889697</v>
+      </c>
+    </row>
+    <row r="316" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A316" s="4">
         <v>563</v>
       </c>
@@ -22905,8 +26699,20 @@
       <c r="U316" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="317" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V316">
+        <v>87</v>
+      </c>
+      <c r="W316">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X316">
+        <v>-1128267.4267698301</v>
+      </c>
+      <c r="Y316">
+        <v>-833018.64685172401</v>
+      </c>
+    </row>
+    <row r="317" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A317" s="4">
         <v>765</v>
       </c>
@@ -22970,8 +26776,20 @@
       <c r="U317" s="11" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="318" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V317">
+        <v>75</v>
+      </c>
+      <c r="W317">
+        <v>4.2</v>
+      </c>
+      <c r="X317">
+        <v>-1130080.40626069</v>
+      </c>
+      <c r="Y317">
+        <v>-821011.07863028406</v>
+      </c>
+    </row>
+    <row r="318" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A318" s="4">
         <v>894</v>
       </c>
@@ -23035,8 +26853,20 @@
       <c r="U318" s="11" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="319" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V318">
+        <v>67</v>
+      </c>
+      <c r="W318">
+        <v>5.7</v>
+      </c>
+      <c r="X318">
+        <v>-1129646.9275464299</v>
+      </c>
+      <c r="Y318">
+        <v>-765776.68341161497</v>
+      </c>
+    </row>
+    <row r="319" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A319" s="4">
         <v>910</v>
       </c>
@@ -23100,8 +26930,20 @@
       <c r="U319" s="11" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="320" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V319">
+        <v>83.5</v>
+      </c>
+      <c r="W319">
+        <v>5.3</v>
+      </c>
+      <c r="X319">
+        <v>-1139226.8448958001</v>
+      </c>
+      <c r="Y319">
+        <v>-693665.71177862899</v>
+      </c>
+    </row>
+    <row r="320" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A320" s="4">
         <v>887</v>
       </c>
@@ -23165,8 +27007,20 @@
       <c r="U320" s="11" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="321" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V320">
+        <v>95</v>
+      </c>
+      <c r="W320">
+        <v>4.2</v>
+      </c>
+      <c r="X320">
+        <v>-1143115.7306196101</v>
+      </c>
+      <c r="Y320">
+        <v>-684986.43943534698</v>
+      </c>
+    </row>
+    <row r="321" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
         <v>937</v>
       </c>
@@ -23230,8 +27084,20 @@
       <c r="U321" s="11" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="322" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V321">
+        <v>66</v>
+      </c>
+      <c r="W321">
+        <v>5.5</v>
+      </c>
+      <c r="X321">
+        <v>-1146057.3080639399</v>
+      </c>
+      <c r="Y321">
+        <v>-660905.36806626397</v>
+      </c>
+    </row>
+    <row r="322" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A322" s="4">
         <v>2169</v>
       </c>
@@ -23295,8 +27161,20 @@
       <c r="U322" s="11" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="323" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V322">
+        <v>66</v>
+      </c>
+      <c r="W322">
+        <v>5.5</v>
+      </c>
+      <c r="X322">
+        <v>-1151215.7609282699</v>
+      </c>
+      <c r="Y322">
+        <v>-664581.22919281095</v>
+      </c>
+    </row>
+    <row r="323" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A323" s="4">
         <v>1905</v>
       </c>
@@ -23360,8 +27238,20 @@
       <c r="U323" s="11" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="324" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V323">
+        <v>75.5</v>
+      </c>
+      <c r="W323">
+        <v>5</v>
+      </c>
+      <c r="X323">
+        <v>-1150610.2054740901</v>
+      </c>
+      <c r="Y323">
+        <v>-621746.87952934206</v>
+      </c>
+    </row>
+    <row r="324" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A324" s="4">
         <v>757</v>
       </c>
@@ -23425,8 +27315,20 @@
       <c r="U324" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="325" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V324">
+        <v>87</v>
+      </c>
+      <c r="W324">
+        <v>4.3</v>
+      </c>
+      <c r="X324">
+        <v>-1132847.6436057801</v>
+      </c>
+      <c r="Y324">
+        <v>-839863.42161809804</v>
+      </c>
+    </row>
+    <row r="325" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A325" s="4">
         <v>739</v>
       </c>
@@ -23490,8 +27392,20 @@
       <c r="U325" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="326" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V325">
+        <v>87</v>
+      </c>
+      <c r="W325">
+        <v>6.3</v>
+      </c>
+      <c r="X325">
+        <v>-1133307.19612856</v>
+      </c>
+      <c r="Y325">
+        <v>-836859.31547548901</v>
+      </c>
+    </row>
+    <row r="326" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A326" s="4">
         <v>834</v>
       </c>
@@ -23555,8 +27469,20 @@
       <c r="U326" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="327" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V326">
+        <v>87</v>
+      </c>
+      <c r="W326">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X326">
+        <v>-1133765.07287634</v>
+      </c>
+      <c r="Y326">
+        <v>-833854.96492009796</v>
+      </c>
+    </row>
+    <row r="327" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A327" s="4">
         <v>539</v>
       </c>
@@ -23620,8 +27546,20 @@
       <c r="U327" s="11" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="328" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V327">
+        <v>84.5</v>
+      </c>
+      <c r="W327">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X327">
+        <v>-1139719.3922310499</v>
+      </c>
+      <c r="Y327">
+        <v>-831683.58943349298</v>
+      </c>
+    </row>
+    <row r="328" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A328" s="4">
         <v>1274</v>
       </c>
@@ -23685,8 +27623,20 @@
       <c r="U328" s="11" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="329" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V328">
+        <v>83</v>
+      </c>
+      <c r="W328">
+        <v>5.6</v>
+      </c>
+      <c r="X328">
+        <v>-1148660.6279483701</v>
+      </c>
+      <c r="Y328">
+        <v>-750012.45094871195</v>
+      </c>
+    </row>
+    <row r="329" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A329" s="4">
         <v>1804</v>
       </c>
@@ -23744,8 +27694,20 @@
       <c r="U329" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="330" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V329">
+        <v>87</v>
+      </c>
+      <c r="W329">
+        <v>5.8</v>
+      </c>
+      <c r="X329">
+        <v>-1158914.6156552399</v>
+      </c>
+      <c r="Y329">
+        <v>-693082.15540185396</v>
+      </c>
+    </row>
+    <row r="330" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A330" s="4">
         <v>932</v>
       </c>
@@ -23809,8 +27771,20 @@
       <c r="U330" s="11" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="331" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V330">
+        <v>95</v>
+      </c>
+      <c r="W330">
+        <v>4.2</v>
+      </c>
+      <c r="X330">
+        <v>-1153775.2612499599</v>
+      </c>
+      <c r="Y330">
+        <v>-689374.55295285</v>
+      </c>
+    </row>
+    <row r="331" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A331" s="4">
         <v>876</v>
       </c>
@@ -23874,8 +27848,20 @@
       <c r="U331" s="11" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="332" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V331">
+        <v>66</v>
+      </c>
+      <c r="W331">
+        <v>4.2</v>
+      </c>
+      <c r="X331">
+        <v>-1153975.9125992099</v>
+      </c>
+      <c r="Y331">
+        <v>-664913.73877420695</v>
+      </c>
+    </row>
+    <row r="332" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
         <v>1669</v>
       </c>
@@ -23939,8 +27925,20 @@
       <c r="U332" s="11" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="333" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V332">
+        <v>77</v>
+      </c>
+      <c r="W332">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X332">
+        <v>-1179743.88164311</v>
+      </c>
+      <c r="Y332">
+        <v>-499542.15624334698</v>
+      </c>
+    </row>
+    <row r="333" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A333" s="4">
         <v>830</v>
       </c>
@@ -24004,8 +28002,20 @@
       <c r="U333" s="11" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="334" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V333">
+        <v>77</v>
+      </c>
+      <c r="W333">
+        <v>4.43</v>
+      </c>
+      <c r="X333">
+        <v>-1177515.7721967101</v>
+      </c>
+      <c r="Y333">
+        <v>-493237.18564947398</v>
+      </c>
+    </row>
+    <row r="334" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A334" s="4">
         <v>538</v>
       </c>
@@ -24069,8 +28079,20 @@
       <c r="U334" s="11" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="335" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V334">
+        <v>84.5</v>
+      </c>
+      <c r="W334">
+        <v>4.5</v>
+      </c>
+      <c r="X334">
+        <v>-1142468.46237446</v>
+      </c>
+      <c r="Y334">
+        <v>-832100.18606195098</v>
+      </c>
+    </row>
+    <row r="335" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A335" s="4">
         <v>751</v>
       </c>
@@ -24134,8 +28156,20 @@
       <c r="U335" s="11" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="336" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V335">
+        <v>84.5</v>
+      </c>
+      <c r="W335">
+        <v>5.3</v>
+      </c>
+      <c r="X335">
+        <v>-1142923.65269462</v>
+      </c>
+      <c r="Y335">
+        <v>-829090.75078164402</v>
+      </c>
+    </row>
+    <row r="336" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A336" s="4">
         <v>1220</v>
       </c>
@@ -24199,8 +28233,20 @@
       <c r="U336" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="337" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V336">
+        <v>91.5</v>
+      </c>
+      <c r="W336">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="X336">
+        <v>-1151625.7476935701</v>
+      </c>
+      <c r="Y336">
+        <v>-827321.61842413596</v>
+      </c>
+    </row>
+    <row r="337" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A337" s="4">
         <v>27</v>
       </c>
@@ -24264,8 +28310,20 @@
       <c r="U337" s="11" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="338" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V337">
+        <v>85.5</v>
+      </c>
+      <c r="W337">
+        <v>5.4</v>
+      </c>
+      <c r="X337">
+        <v>-1144727.63954091</v>
+      </c>
+      <c r="Y337">
+        <v>-817050.60151306004</v>
+      </c>
+    </row>
+    <row r="338" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A338" s="4">
         <v>787</v>
       </c>
@@ -24329,8 +28387,20 @@
       <c r="U338" s="11" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="339" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V338">
+        <v>85.5</v>
+      </c>
+      <c r="W338">
+        <v>5.6</v>
+      </c>
+      <c r="X338">
+        <v>-1147477.81532886</v>
+      </c>
+      <c r="Y338">
+        <v>-817459.528690623</v>
+      </c>
+    </row>
+    <row r="339" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A339" s="4">
         <v>806</v>
       </c>
@@ -24394,8 +28464,20 @@
       <c r="U339" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="340" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V339">
+        <v>91.5</v>
+      </c>
+      <c r="W339">
+        <v>13</v>
+      </c>
+      <c r="X339">
+        <v>-1153425.6443866401</v>
+      </c>
+      <c r="Y339">
+        <v>-815262.12734337698</v>
+      </c>
+    </row>
+    <row r="340" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A340" s="4">
         <v>131</v>
       </c>
@@ -24459,8 +28541,20 @@
       <c r="U340" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="341" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V340">
+        <v>91.5</v>
+      </c>
+      <c r="W340">
+        <v>10.8</v>
+      </c>
+      <c r="X340">
+        <v>-1153871.4206343901</v>
+      </c>
+      <c r="Y340">
+        <v>-812246.659288925</v>
+      </c>
+    </row>
+    <row r="341" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A341" s="4">
         <v>851</v>
       </c>
@@ -24524,8 +28618,20 @@
       <c r="U341" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="342" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V341">
+        <v>91.5</v>
+      </c>
+      <c r="W341">
+        <v>11.6</v>
+      </c>
+      <c r="X341">
+        <v>-1150134.78201678</v>
+      </c>
+      <c r="Y341">
+        <v>-799382.97800137603</v>
+      </c>
+    </row>
+    <row r="342" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A342" s="4">
         <v>817</v>
       </c>
@@ -24589,8 +28695,20 @@
       <c r="U342" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="343" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V342">
+        <v>87</v>
+      </c>
+      <c r="W342">
+        <v>5.7</v>
+      </c>
+      <c r="X342">
+        <v>-1157743.5986204999</v>
+      </c>
+      <c r="Y342">
+        <v>-745103.60927212995</v>
+      </c>
+    </row>
+    <row r="343" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
         <v>2128</v>
       </c>
@@ -24654,8 +28772,20 @@
       <c r="U343" s="11" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="344" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V343">
+        <v>83</v>
+      </c>
+      <c r="W343">
+        <v>5.5</v>
+      </c>
+      <c r="X343">
+        <v>-1164101.47518653</v>
+      </c>
+      <c r="Y343">
+        <v>-718295.49006597803</v>
+      </c>
+    </row>
+    <row r="344" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A344" s="4">
         <v>2127</v>
       </c>
@@ -24719,8 +28849,20 @@
       <c r="U344" s="11" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="345" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V344">
+        <v>83</v>
+      </c>
+      <c r="W344">
+        <v>5.2</v>
+      </c>
+      <c r="X344">
+        <v>-1166858.43027446</v>
+      </c>
+      <c r="Y344">
+        <v>-718653.92360094399</v>
+      </c>
+    </row>
+    <row r="345" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A345" s="4">
         <v>922</v>
       </c>
@@ -24778,8 +28920,20 @@
       <c r="U345" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="346" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V345">
+        <v>87</v>
+      </c>
+      <c r="W345">
+        <v>5.3</v>
+      </c>
+      <c r="X345">
+        <v>-1160143.70394087</v>
+      </c>
+      <c r="Y345">
+        <v>-705505.16191265697</v>
+      </c>
+    </row>
+    <row r="346" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A346" s="4">
         <v>897</v>
       </c>
@@ -24837,8 +28991,20 @@
       <c r="U346" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="347" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V346">
+        <v>87</v>
+      </c>
+      <c r="W346">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X346">
+        <v>-1163286.4685981499</v>
+      </c>
+      <c r="Y346">
+        <v>-702837.084904016</v>
+      </c>
+    </row>
+    <row r="347" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A347" s="4">
         <v>926</v>
       </c>
@@ -24902,8 +29068,20 @@
       <c r="U347" s="11" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="348" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V347" t="s">
+        <v>627</v>
+      </c>
+      <c r="W347">
+        <v>4.8</v>
+      </c>
+      <c r="X347">
+        <v>-1170900.20788009</v>
+      </c>
+      <c r="Y347">
+        <v>-663884.15758673102</v>
+      </c>
+    </row>
+    <row r="348" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A348" s="4">
         <v>777</v>
       </c>
@@ -24967,8 +29145,20 @@
       <c r="U348" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="349" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V348">
+        <v>91.5</v>
+      </c>
+      <c r="W348">
+        <v>12.7</v>
+      </c>
+      <c r="X348">
+        <v>-1154375.2918602901</v>
+      </c>
+      <c r="Y348">
+        <v>-827735.11600255896</v>
+      </c>
+    </row>
+    <row r="349" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A349" s="4">
         <v>748</v>
       </c>
@@ -25032,8 +29222,20 @@
       <c r="U349" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="350" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V349">
+        <v>91.5</v>
+      </c>
+      <c r="W349">
+        <v>14</v>
+      </c>
+      <c r="X349">
+        <v>-1155279.0363560701</v>
+      </c>
+      <c r="Y349">
+        <v>-821702.78439321998</v>
+      </c>
+    </row>
+    <row r="350" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A350" s="4">
         <v>789</v>
       </c>
@@ -25097,8 +29299,20 @@
       <c r="U350" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="351" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V350">
+        <v>91.5</v>
+      </c>
+      <c r="W350">
+        <v>11.7</v>
+      </c>
+      <c r="X350">
+        <v>-1155728.3880803101</v>
+      </c>
+      <c r="Y350">
+        <v>-818686.25988875201</v>
+      </c>
+    </row>
+    <row r="351" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A351" s="4">
         <v>805</v>
       </c>
@@ -25162,8 +29376,20 @@
       <c r="U351" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="352" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V351">
+        <v>91.5</v>
+      </c>
+      <c r="W351">
+        <v>15.4</v>
+      </c>
+      <c r="X351">
+        <v>-1161676.91616253</v>
+      </c>
+      <c r="Y351">
+        <v>-816484.21299181797</v>
+      </c>
+    </row>
+    <row r="352" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A352" s="4">
         <v>50</v>
       </c>
@@ -25227,8 +29453,20 @@
       <c r="U352" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="353" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V352">
+        <v>91.5</v>
+      </c>
+      <c r="W352">
+        <v>11.2</v>
+      </c>
+      <c r="X352">
+        <v>-1162568.0814324699</v>
+      </c>
+      <c r="Y352">
+        <v>-810443.85329530097</v>
+      </c>
+    </row>
+    <row r="353" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A353" s="4">
         <v>850</v>
       </c>
@@ -25292,8 +29530,20 @@
       <c r="U353" s="11" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="354" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V353">
+        <v>85.5</v>
+      </c>
+      <c r="W353">
+        <v>6</v>
+      </c>
+      <c r="X353">
+        <v>-1161140.72050832</v>
+      </c>
+      <c r="Y353">
+        <v>-800981.85255369602</v>
+      </c>
+    </row>
+    <row r="354" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
         <v>790</v>
       </c>
@@ -25357,8 +29607,20 @@
       <c r="U354" s="11" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="355" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V354">
+        <v>85.5</v>
+      </c>
+      <c r="W354">
+        <v>5.4</v>
+      </c>
+      <c r="X354">
+        <v>-1159696.97451134</v>
+      </c>
+      <c r="Y354">
+        <v>-791526.93153857696</v>
+      </c>
+    </row>
+    <row r="355" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A355" s="4">
         <v>793</v>
       </c>
@@ -25422,8 +29684,20 @@
       <c r="U355" s="11" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="356" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V355">
+        <v>85.5</v>
+      </c>
+      <c r="W355">
+        <v>5.4</v>
+      </c>
+      <c r="X355">
+        <v>-1162014.65500393</v>
+      </c>
+      <c r="Y355">
+        <v>-794942.21344548196</v>
+      </c>
+    </row>
+    <row r="356" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A356" s="4">
         <v>390</v>
       </c>
@@ -25487,8 +29761,20 @@
       <c r="U356" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="357" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V356">
+        <v>87</v>
+      </c>
+      <c r="W356">
+        <v>4.3</v>
+      </c>
+      <c r="X356">
+        <v>-1170102.5120023601</v>
+      </c>
+      <c r="Y356">
+        <v>-777592.67847050901</v>
+      </c>
+    </row>
+    <row r="357" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A357" s="4">
         <v>666</v>
       </c>
@@ -25552,8 +29838,20 @@
       <c r="U357" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="358" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V357">
+        <v>87</v>
+      </c>
+      <c r="W357">
+        <v>4</v>
+      </c>
+      <c r="X357">
+        <v>-1168618.0301226301</v>
+      </c>
+      <c r="Y357">
+        <v>-768135.35105357401</v>
+      </c>
+    </row>
+    <row r="358" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A358" s="4">
         <v>2126</v>
       </c>
@@ -25617,8 +29915,20 @@
       <c r="U358" s="11" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="359" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V358">
+        <v>83</v>
+      </c>
+      <c r="W358">
+        <v>4.7</v>
+      </c>
+      <c r="X358">
+        <v>-1169615.38617308</v>
+      </c>
+      <c r="Y358">
+        <v>-719012.35177027294</v>
+      </c>
+    </row>
+    <row r="359" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A359" s="4">
         <v>1402</v>
       </c>
@@ -25676,8 +29986,20 @@
       <c r="U359" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="360" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V359">
+        <v>87</v>
+      </c>
+      <c r="W359">
+        <v>5.7</v>
+      </c>
+      <c r="X359">
+        <v>-1174318.10309293</v>
+      </c>
+      <c r="Y359">
+        <v>-704240.26446192304</v>
+      </c>
+    </row>
+    <row r="360" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A360" s="4">
         <v>107</v>
       </c>
@@ -25741,8 +30063,20 @@
       <c r="U360" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="361" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V360">
+        <v>91.5</v>
+      </c>
+      <c r="W360">
+        <v>10.5</v>
+      </c>
+      <c r="X360">
+        <v>-1168955.1278115101</v>
+      </c>
+      <c r="Y360">
+        <v>-805204.98616920598</v>
+      </c>
+    </row>
+    <row r="361" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A361" s="4">
         <v>849</v>
       </c>
@@ -25806,8 +30140,20 @@
       <c r="U361" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="362" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V361">
+        <v>91.5</v>
+      </c>
+      <c r="W361">
+        <v>10</v>
+      </c>
+      <c r="X361">
+        <v>-1169395.2517608299</v>
+      </c>
+      <c r="Y361">
+        <v>-802180.92375325004</v>
+      </c>
+    </row>
+    <row r="362" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A362" s="4">
         <v>165</v>
       </c>
@@ -25871,8 +30217,20 @@
       <c r="U362" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="363" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V362">
+        <v>91.5</v>
+      </c>
+      <c r="W362">
+        <v>8.5</v>
+      </c>
+      <c r="X362">
+        <v>-1169833.6935086299</v>
+      </c>
+      <c r="Y362">
+        <v>-799156.62869934703</v>
+      </c>
+    </row>
+    <row r="363" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A363" s="4">
         <v>848</v>
       </c>
@@ -25936,8 +30294,20 @@
       <c r="U363" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="364" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V363">
+        <v>91.5</v>
+      </c>
+      <c r="W363">
+        <v>10.3</v>
+      </c>
+      <c r="X363">
+        <v>-1174898.3154430501</v>
+      </c>
+      <c r="Y363">
+        <v>-802980.26209747803</v>
+      </c>
+    </row>
+    <row r="364" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A364" s="4">
         <v>878</v>
       </c>
@@ -26001,8 +30371,20 @@
       <c r="U364" s="11" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="365" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V364">
+        <v>87</v>
+      </c>
+      <c r="W364">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X364">
+        <v>-1171570.64299988</v>
+      </c>
+      <c r="Y364">
+        <v>-787057.13948423299</v>
+      </c>
+    </row>
+    <row r="365" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
         <v>774</v>
       </c>
@@ -26066,8 +30448,20 @@
       <c r="U365" s="11" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="366" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V365">
+        <v>87</v>
+      </c>
+      <c r="W365">
+        <v>4.7</v>
+      </c>
+      <c r="X365">
+        <v>-1173891.2954673499</v>
+      </c>
+      <c r="Y365">
+        <v>-790475.90944098798</v>
+      </c>
+    </row>
+    <row r="366" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A366" s="4">
         <v>771</v>
       </c>
@@ -26131,8 +30525,20 @@
       <c r="U366" s="11" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="367" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V366">
+        <v>87</v>
+      </c>
+      <c r="W366">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X366">
+        <v>-1176643.6711357799</v>
+      </c>
+      <c r="Y366">
+        <v>-790869.45452059398</v>
+      </c>
+    </row>
+    <row r="367" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A367" s="4">
         <v>389</v>
       </c>
@@ -26196,8 +30602,20 @@
       <c r="U367" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="368" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V367">
+        <v>91.5</v>
+      </c>
+      <c r="W367">
+        <v>7</v>
+      </c>
+      <c r="X367">
+        <v>-1172855.70051667</v>
+      </c>
+      <c r="Y367">
+        <v>-777980.12073509803</v>
+      </c>
+    </row>
+    <row r="368" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A368" s="4">
         <v>1654</v>
       </c>
@@ -26261,8 +30679,20 @@
       <c r="U368" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="369" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V368">
+        <v>87</v>
+      </c>
+      <c r="W368">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X368">
+        <v>-1173280.69081051</v>
+      </c>
+      <c r="Y368">
+        <v>-774953.99450481602</v>
+      </c>
+    </row>
+    <row r="369" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A369" s="4">
         <v>918</v>
       </c>
@@ -26326,8 +30756,20 @@
       <c r="U369" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="370" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V369">
+        <v>91.5</v>
+      </c>
+      <c r="W369">
+        <v>10.1</v>
+      </c>
+      <c r="X369">
+        <v>-1176034.09113373</v>
+      </c>
+      <c r="Y369">
+        <v>-775339.89990006899</v>
+      </c>
+    </row>
+    <row r="370" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A370" s="4">
         <v>1385</v>
       </c>
@@ -26391,8 +30833,20 @@
       <c r="U370" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="371" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V370">
+        <v>87</v>
+      </c>
+      <c r="W370">
+        <v>6</v>
+      </c>
+      <c r="X370">
+        <v>-1173704.0002126801</v>
+      </c>
+      <c r="Y370">
+        <v>-771927.64326672698</v>
+      </c>
+    </row>
+    <row r="371" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A371" s="4">
         <v>1281</v>
       </c>
@@ -26456,8 +30910,20 @@
       <c r="U371" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="372" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V371">
+        <v>87</v>
+      </c>
+      <c r="W371">
+        <v>5.6</v>
+      </c>
+      <c r="X371">
+        <v>-1174545.5770536</v>
+      </c>
+      <c r="Y371">
+        <v>-765874.26784432901</v>
+      </c>
+    </row>
+    <row r="372" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A372" s="4">
         <v>931</v>
       </c>
@@ -26521,8 +30987,20 @@
       <c r="U372" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="373" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V372">
+        <v>87</v>
+      </c>
+      <c r="W372">
+        <v>4.2</v>
+      </c>
+      <c r="X372">
+        <v>-1180643.2256380499</v>
+      </c>
+      <c r="Y372">
+        <v>-720446.00637886696</v>
+      </c>
+    </row>
+    <row r="373" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A373" s="4">
         <v>802</v>
       </c>
@@ -26586,8 +31064,20 @@
       <c r="U373" s="11" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="374" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V373">
+        <v>91.5</v>
+      </c>
+      <c r="W373">
+        <v>14.4</v>
+      </c>
+      <c r="X373">
+        <v>-1180840.70322896</v>
+      </c>
+      <c r="Y373">
+        <v>-800749.15034063405</v>
+      </c>
+    </row>
+    <row r="374" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A374" s="4">
         <v>916</v>
       </c>
@@ -26651,8 +31141,20 @@
       <c r="U374" s="11" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="375" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V374">
+        <v>87</v>
+      </c>
+      <c r="W374">
+        <v>4</v>
+      </c>
+      <c r="X374">
+        <v>-1189801.2125712601</v>
+      </c>
+      <c r="Y374">
+        <v>-777269.30794623098</v>
+      </c>
+    </row>
+    <row r="375" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A375" s="4">
         <v>386</v>
       </c>
@@ -26716,8 +31218,20 @@
       <c r="U375" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="376" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V375">
+        <v>87</v>
+      </c>
+      <c r="W375">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X375">
+        <v>-1192128.2413379501</v>
+      </c>
+      <c r="Y375">
+        <v>-780691.99426393502</v>
+      </c>
+    </row>
+    <row r="376" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
         <v>935</v>
       </c>
@@ -26781,8 +31295,20 @@
       <c r="U376" s="11" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="377" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V376">
+        <v>87</v>
+      </c>
+      <c r="W376">
+        <v>4.7</v>
+      </c>
+      <c r="X376">
+        <v>-1188734.98336616</v>
+      </c>
+      <c r="Y376">
+        <v>-764746.11720373703</v>
+      </c>
+    </row>
+    <row r="377" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A377" s="4">
         <v>2095</v>
       </c>
@@ -26846,8 +31372,20 @@
       <c r="U377" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="378" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V377">
+        <v>87</v>
+      </c>
+      <c r="W377">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X377">
+        <v>-1189152.5758413</v>
+      </c>
+      <c r="Y377">
+        <v>-761711.23073950503</v>
+      </c>
+    </row>
+    <row r="378" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A378" s="4">
         <v>1290</v>
       </c>
@@ -26911,8 +31449,20 @@
       <c r="U378" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="379" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V378">
+        <v>87</v>
+      </c>
+      <c r="W378">
+        <v>4.5</v>
+      </c>
+      <c r="X378">
+        <v>-1195077.7934737301</v>
+      </c>
+      <c r="Y378">
+        <v>-759429.50567018404</v>
+      </c>
+    </row>
+    <row r="379" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A379" s="4">
         <v>913</v>
       </c>
@@ -26976,8 +31526,20 @@
       <c r="U379" s="11" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="380" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V379">
+        <v>87</v>
+      </c>
+      <c r="W379">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X379">
+        <v>-1196726.1736646099</v>
+      </c>
+      <c r="Y379">
+        <v>-747274.66709858098</v>
+      </c>
+    </row>
+    <row r="380" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A380" s="4">
         <v>796</v>
       </c>
@@ -27041,8 +31603,20 @@
       <c r="U380" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="381" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V380">
+        <v>87</v>
+      </c>
+      <c r="W380">
+        <v>4.5</v>
+      </c>
+      <c r="X380">
+        <v>-1196776.0438816301</v>
+      </c>
+      <c r="Y380">
+        <v>-787545.83816854097</v>
+      </c>
+    </row>
+    <row r="381" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A381" s="4">
         <v>823</v>
       </c>
@@ -27106,8 +31680,20 @@
       <c r="U381" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="382" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V381">
+        <v>87</v>
+      </c>
+      <c r="W381">
+        <v>4.2</v>
+      </c>
+      <c r="X381">
+        <v>-1200388.04324789</v>
+      </c>
+      <c r="Y381">
+        <v>-781854.10078095098</v>
+      </c>
+    </row>
+    <row r="382" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A382" s="4">
         <v>1377</v>
       </c>
@@ -27171,8 +31757,20 @@
       <c r="U382" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="383" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V382">
+        <v>87</v>
+      </c>
+      <c r="W382">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X382">
+        <v>-1201240.4200889701</v>
+      </c>
+      <c r="Y382">
+        <v>-775771.04635944602</v>
+      </c>
+    </row>
+    <row r="383" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A383" s="4">
         <v>1818</v>
       </c>
@@ -27236,8 +31834,20 @@
       <c r="U383" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="384" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V383">
+        <v>87</v>
+      </c>
+      <c r="W383">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X383">
+        <v>-1199752.0370904901</v>
+      </c>
+      <c r="Y383">
+        <v>-766265.07484785304</v>
+      </c>
+    </row>
+    <row r="384" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A384" s="4">
         <v>865</v>
       </c>
@@ -27301,8 +31911,20 @@
       <c r="U384" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="385" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V384">
+        <v>87</v>
+      </c>
+      <c r="W384">
+        <v>4.7</v>
+      </c>
+      <c r="X384">
+        <v>-1204992.5679923601</v>
+      </c>
+      <c r="Y384">
+        <v>-748386.35007425596</v>
+      </c>
+    </row>
+    <row r="385" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A385" s="4">
         <v>873</v>
       </c>
@@ -27366,8 +31988,20 @@
       <c r="U385" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="386" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V385">
+        <v>87</v>
+      </c>
+      <c r="W385">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X385">
+        <v>-1202645.36856947</v>
+      </c>
+      <c r="Y385">
+        <v>-744973.48994100501</v>
+      </c>
+    </row>
+    <row r="386" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A386" s="4">
         <v>753</v>
       </c>
@@ -27431,8 +32065,20 @@
       <c r="U386" s="11" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="387" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V386">
+        <v>87</v>
+      </c>
+      <c r="W386">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X386">
+        <v>-1207171.87972231</v>
+      </c>
+      <c r="Y386">
+        <v>-773494.70828989299</v>
+      </c>
+    </row>
+    <row r="387" spans="1:25" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A387" s="6">
         <v>872</v>
       </c>
@@ -27496,15 +32142,21 @@
       <c r="U387" s="14" t="s">
         <v>130</v>
       </c>
+      <c r="V387">
+        <v>87</v>
+      </c>
+      <c r="W387">
+        <v>3.6</v>
+      </c>
+      <c r="X387">
+        <v>-1210912.39978113</v>
+      </c>
+      <c r="Y387">
+        <v>-746080.54532296804</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U387">
-    <filterColumn colId="15">
-      <filters>
-        <dateGroupItem year="2025" dateTimeGrouping="year"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Y1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>